--- a/research/traditional_assets/database/data/nigeria/nigeria_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_furn_home_furnishings.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1798232631958509</v>
+        <v>0.1793152934062633</v>
       </c>
       <c r="C2">
-        <v>27.46049082838837</v>
+        <v>27.27275440081616</v>
       </c>
       <c r="D2">
-        <v>22.20049082838837</v>
+        <v>22.28495440081616</v>
       </c>
       <c r="E2">
-        <v>-8.52</v>
+        <v>-8.2478</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2722</v>
       </c>
       <c r="G2">
         <v>5.26</v>
@@ -1445,28 +1445,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01369166</v>
       </c>
       <c r="N2">
-        <v>7.673333333333334</v>
+        <v>7.659641673333334</v>
       </c>
       <c r="O2">
-        <v>2.302</v>
+        <v>2.297892502</v>
       </c>
       <c r="P2">
-        <v>5.371333333333334</v>
+        <v>5.361749171333334</v>
       </c>
       <c r="Q2">
-        <v>6.031333333333334</v>
+        <v>6.021749171333334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1798232631958509</v>
+        <v>0.180770902430569</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460946</v>
+        <v>0.9410768637728851</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>560.4384956486894</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1793152934062633</v>
+        <v>0.1788073236166758</v>
       </c>
       <c r="C3">
-        <v>27.27275440081616</v>
+        <v>27.08566312483331</v>
       </c>
       <c r="D3">
-        <v>22.28495440081616</v>
+        <v>22.37006312483331</v>
       </c>
       <c r="E3">
-        <v>-8.2478</v>
+        <v>-7.9756</v>
       </c>
       <c r="F3">
-        <v>0.2722</v>
+        <v>0.5444</v>
       </c>
       <c r="G3">
         <v>5.26</v>
@@ -1527,28 +1527,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M3">
-        <v>0.01369166</v>
+        <v>0.02738332</v>
       </c>
       <c r="N3">
-        <v>7.659641673333334</v>
+        <v>7.645950013333334</v>
       </c>
       <c r="O3">
-        <v>2.297892502</v>
+        <v>2.293785004</v>
       </c>
       <c r="P3">
-        <v>5.361749171333334</v>
+        <v>5.352165009333334</v>
       </c>
       <c r="Q3">
-        <v>6.021749171333334</v>
+        <v>6.012165009333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.180770902430569</v>
+        <v>0.1817378812415059</v>
       </c>
       <c r="T3">
-        <v>0.9410768637728851</v>
+        <v>0.9478190679838959</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>560.4384956486894</v>
+        <v>280.2192478243447</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1788073236166758</v>
+        <v>0.1782993538270882</v>
       </c>
       <c r="C4">
-        <v>27.08566312483331</v>
+        <v>26.89922442049524</v>
       </c>
       <c r="D4">
-        <v>22.37006312483331</v>
+        <v>22.45582442049525</v>
       </c>
       <c r="E4">
-        <v>-7.9756</v>
+        <v>-7.703399999999999</v>
       </c>
       <c r="F4">
-        <v>0.5444</v>
+        <v>0.8165999999999999</v>
       </c>
       <c r="G4">
         <v>5.26</v>
@@ -1609,28 +1609,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M4">
-        <v>0.02738332</v>
+        <v>0.04107497999999999</v>
       </c>
       <c r="N4">
-        <v>7.645950013333334</v>
+        <v>7.632258353333333</v>
       </c>
       <c r="O4">
-        <v>2.293785004</v>
+        <v>2.289677506</v>
       </c>
       <c r="P4">
-        <v>5.352165009333334</v>
+        <v>5.342580847333334</v>
       </c>
       <c r="Q4">
-        <v>6.012165009333334</v>
+        <v>6.002580847333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1817378812415059</v>
+        <v>0.1827247977598848</v>
       </c>
       <c r="T4">
-        <v>0.9478190679838959</v>
+        <v>0.9547002867147213</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>280.2192478243447</v>
+        <v>186.8128318828965</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1782993538270882</v>
+        <v>0.1777913840375007</v>
       </c>
       <c r="C5">
-        <v>26.89922442049524</v>
+        <v>26.71344582208199</v>
       </c>
       <c r="D5">
-        <v>22.45582442049525</v>
+        <v>22.54224582208199</v>
       </c>
       <c r="E5">
-        <v>-7.703399999999999</v>
+        <v>-7.4312</v>
       </c>
       <c r="F5">
-        <v>0.8165999999999999</v>
+        <v>1.0888</v>
       </c>
       <c r="G5">
         <v>5.26</v>
@@ -1691,28 +1691,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M5">
-        <v>0.04107497999999999</v>
+        <v>0.05476664</v>
       </c>
       <c r="N5">
-        <v>7.632258353333333</v>
+        <v>7.618566693333333</v>
       </c>
       <c r="O5">
-        <v>2.289677506</v>
+        <v>2.285570008</v>
       </c>
       <c r="P5">
-        <v>5.342580847333334</v>
+        <v>5.332996685333333</v>
       </c>
       <c r="Q5">
-        <v>6.002580847333334</v>
+        <v>5.992996685333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1827247977598848</v>
+        <v>0.1837322750390632</v>
       </c>
       <c r="T5">
-        <v>0.9547002867147213</v>
+        <v>0.9617248641691056</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>186.8128318828965</v>
+        <v>140.1096239121723</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1777913840375007</v>
+        <v>0.1772834142479131</v>
       </c>
       <c r="C6">
-        <v>26.71344582208199</v>
+        <v>26.5283349803045</v>
       </c>
       <c r="D6">
-        <v>22.54224582208199</v>
+        <v>22.62933498030451</v>
       </c>
       <c r="E6">
-        <v>-7.4312</v>
+        <v>-7.159</v>
       </c>
       <c r="F6">
-        <v>1.0888</v>
+        <v>1.361</v>
       </c>
       <c r="G6">
         <v>5.26</v>
@@ -1773,28 +1773,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M6">
-        <v>0.05476664</v>
+        <v>0.0684583</v>
       </c>
       <c r="N6">
-        <v>7.618566693333333</v>
+        <v>7.604875033333334</v>
       </c>
       <c r="O6">
-        <v>2.285570008</v>
+        <v>2.28146251</v>
       </c>
       <c r="P6">
-        <v>5.332996685333333</v>
+        <v>5.323412523333333</v>
       </c>
       <c r="Q6">
-        <v>5.992996685333333</v>
+        <v>5.983412523333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1837322750390632</v>
+        <v>0.1847609623662243</v>
       </c>
       <c r="T6">
-        <v>0.9617248641691056</v>
+        <v>0.9688973274646349</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>140.1096239121723</v>
+        <v>112.0876991297379</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1772834142479131</v>
+        <v>0.1767754444583255</v>
       </c>
       <c r="C7">
-        <v>26.5283349803045</v>
+        <v>26.34389966456262</v>
       </c>
       <c r="D7">
-        <v>22.62933498030451</v>
+        <v>22.71709966456262</v>
       </c>
       <c r="E7">
-        <v>-7.159</v>
+        <v>-6.886799999999999</v>
       </c>
       <c r="F7">
-        <v>1.361</v>
+        <v>1.6332</v>
       </c>
       <c r="G7">
         <v>5.26</v>
@@ -1855,28 +1855,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M7">
-        <v>0.0684583</v>
+        <v>0.08214995999999999</v>
       </c>
       <c r="N7">
-        <v>7.604875033333334</v>
+        <v>7.591183373333334</v>
       </c>
       <c r="O7">
-        <v>2.28146251</v>
+        <v>2.277355012</v>
       </c>
       <c r="P7">
-        <v>5.323412523333333</v>
+        <v>5.313828361333334</v>
       </c>
       <c r="Q7">
-        <v>5.983412523333334</v>
+        <v>5.973828361333334</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1847609623662243</v>
+        <v>0.1858115366577932</v>
       </c>
       <c r="T7">
-        <v>0.9688973274646349</v>
+        <v>0.9762223963621967</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>112.0876991297379</v>
+        <v>93.40641594144823</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1767754444583255</v>
+        <v>0.176267474668738</v>
       </c>
       <c r="C8">
-        <v>26.34389966456262</v>
+        <v>26.16014776525551</v>
       </c>
       <c r="D8">
-        <v>22.71709966456262</v>
+        <v>22.80554776525551</v>
       </c>
       <c r="E8">
-        <v>-6.8868</v>
+        <v>-6.614599999999999</v>
       </c>
       <c r="F8">
-        <v>1.6332</v>
+        <v>1.9054</v>
       </c>
       <c r="G8">
         <v>5.26</v>
@@ -1937,28 +1937,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M8">
-        <v>0.08214995999999998</v>
+        <v>0.09584161999999999</v>
       </c>
       <c r="N8">
-        <v>7.591183373333334</v>
+        <v>7.577491713333334</v>
       </c>
       <c r="O8">
-        <v>2.277355012</v>
+        <v>2.273247514</v>
       </c>
       <c r="P8">
-        <v>5.313828361333334</v>
+        <v>5.304244199333334</v>
       </c>
       <c r="Q8">
-        <v>5.973828361333334</v>
+        <v>5.964244199333335</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1858115366577932</v>
+        <v>0.1868847039448796</v>
       </c>
       <c r="T8">
-        <v>0.9762223963621967</v>
+        <v>0.9837049936231469</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>93.40641594144824</v>
+        <v>80.06264223552706</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.176267474668738</v>
+        <v>0.1757595048791505</v>
       </c>
       <c r="C9">
-        <v>26.16014776525551</v>
+        <v>25.97708729614644</v>
       </c>
       <c r="D9">
-        <v>22.80554776525551</v>
+        <v>22.89468729614644</v>
       </c>
       <c r="E9">
-        <v>-6.614599999999999</v>
+        <v>-6.3424</v>
       </c>
       <c r="F9">
-        <v>1.9054</v>
+        <v>2.1776</v>
       </c>
       <c r="G9">
         <v>5.26</v>
@@ -2019,28 +2019,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M9">
-        <v>0.09584162</v>
+        <v>0.10953328</v>
       </c>
       <c r="N9">
-        <v>7.577491713333334</v>
+        <v>7.563800053333334</v>
       </c>
       <c r="O9">
-        <v>2.273247514</v>
+        <v>2.269140016</v>
       </c>
       <c r="P9">
-        <v>5.304244199333334</v>
+        <v>5.294660037333333</v>
       </c>
       <c r="Q9">
-        <v>5.964244199333335</v>
+        <v>5.954660037333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1868847039448796</v>
+        <v>0.1879812009555983</v>
       </c>
       <c r="T9">
-        <v>0.9837049936231469</v>
+        <v>0.9913502560419439</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>80.06264223552705</v>
+        <v>70.05481195608617</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1757595048791505</v>
+        <v>0.1752515350895629</v>
       </c>
       <c r="C10">
-        <v>25.97708729614644</v>
+        <v>25.79472639678322</v>
       </c>
       <c r="D10">
-        <v>22.89468729614644</v>
+        <v>22.98452639678322</v>
       </c>
       <c r="E10">
-        <v>-6.3424</v>
+        <v>-6.0702</v>
       </c>
       <c r="F10">
-        <v>2.1776</v>
+        <v>2.4498</v>
       </c>
       <c r="G10">
         <v>5.26</v>
@@ -2101,28 +2101,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M10">
-        <v>0.10953328</v>
+        <v>0.12322494</v>
       </c>
       <c r="N10">
-        <v>7.563800053333334</v>
+        <v>7.550108393333334</v>
       </c>
       <c r="O10">
-        <v>2.269140016</v>
+        <v>2.265032518</v>
       </c>
       <c r="P10">
-        <v>5.294660037333333</v>
+        <v>5.285075875333334</v>
       </c>
       <c r="Q10">
-        <v>5.954660037333333</v>
+        <v>5.945075875333334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1879812009555983</v>
+        <v>0.1891017968017175</v>
       </c>
       <c r="T10">
-        <v>0.9913502560419439</v>
+        <v>0.9991635462062088</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>70.05481195608617</v>
+        <v>62.27094396096549</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1752515350895629</v>
+        <v>0.1747435652999754</v>
       </c>
       <c r="C11">
-        <v>25.79472639678322</v>
+        <v>25.61307333497577</v>
       </c>
       <c r="D11">
-        <v>22.98452639678322</v>
+        <v>23.07507333497577</v>
       </c>
       <c r="E11">
-        <v>-6.0702</v>
+        <v>-5.798</v>
       </c>
       <c r="F11">
-        <v>2.4498</v>
+        <v>2.722</v>
       </c>
       <c r="G11">
         <v>5.26</v>
@@ -2183,28 +2183,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M11">
-        <v>0.12322494</v>
+        <v>0.1369166</v>
       </c>
       <c r="N11">
-        <v>7.550108393333334</v>
+        <v>7.536416733333334</v>
       </c>
       <c r="O11">
-        <v>2.265032518</v>
+        <v>2.26092502</v>
       </c>
       <c r="P11">
-        <v>5.285075875333334</v>
+        <v>5.275491713333333</v>
       </c>
       <c r="Q11">
-        <v>5.945075875333334</v>
+        <v>5.935491713333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1891017968017175</v>
+        <v>0.1902472947777504</v>
       </c>
       <c r="T11">
-        <v>0.9991635462062088</v>
+        <v>1.007150465040791</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>62.27094396096549</v>
+        <v>56.04384956486894</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1747435652999754</v>
+        <v>0.1742355955103878</v>
       </c>
       <c r="C12">
-        <v>25.61307333497577</v>
+        <v>25.43213650933258</v>
       </c>
       <c r="D12">
-        <v>23.07507333497577</v>
+        <v>23.16633650933258</v>
       </c>
       <c r="E12">
-        <v>-5.798</v>
+        <v>-5.5258</v>
       </c>
       <c r="F12">
-        <v>2.722</v>
+        <v>2.9942</v>
       </c>
       <c r="G12">
         <v>5.26</v>
@@ -2265,28 +2265,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M12">
-        <v>0.1369166</v>
+        <v>0.15060826</v>
       </c>
       <c r="N12">
-        <v>7.536416733333334</v>
+        <v>7.522725073333334</v>
       </c>
       <c r="O12">
-        <v>2.26092502</v>
+        <v>2.256817522</v>
       </c>
       <c r="P12">
-        <v>5.275491713333333</v>
+        <v>5.265907551333333</v>
       </c>
       <c r="Q12">
-        <v>5.935491713333334</v>
+        <v>5.925907551333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1902472947777504</v>
+        <v>0.1914185342813346</v>
       </c>
       <c r="T12">
-        <v>1.007150465040791</v>
+        <v>1.015316865197498</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>56.04384956486894</v>
+        <v>50.94895414988085</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1742355955103878</v>
+        <v>0.1737276257208002</v>
       </c>
       <c r="C13">
-        <v>25.43213650933258</v>
+        <v>25.25192445185754</v>
       </c>
       <c r="D13">
-        <v>23.16633650933258</v>
+        <v>23.25832445185754</v>
       </c>
       <c r="E13">
-        <v>-5.5258</v>
+        <v>-5.2536</v>
       </c>
       <c r="F13">
-        <v>2.9942</v>
+        <v>3.2664</v>
       </c>
       <c r="G13">
         <v>5.26</v>
@@ -2347,28 +2347,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M13">
-        <v>0.15060826</v>
+        <v>0.16429992</v>
       </c>
       <c r="N13">
-        <v>7.522725073333334</v>
+        <v>7.509033413333333</v>
       </c>
       <c r="O13">
-        <v>2.256817522</v>
+        <v>2.252710024</v>
       </c>
       <c r="P13">
-        <v>5.265907551333333</v>
+        <v>5.256323389333334</v>
       </c>
       <c r="Q13">
-        <v>5.925907551333333</v>
+        <v>5.916323389333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1914185342813346</v>
+        <v>0.1926163928645457</v>
       </c>
       <c r="T13">
-        <v>1.015316865197498</v>
+        <v>1.023668865357767</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>50.94895414988085</v>
+        <v>46.70320797072412</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1737276257208002</v>
+        <v>0.1732196559312127</v>
       </c>
       <c r="C14">
-        <v>25.25192445185754</v>
+        <v>25.07244583060892</v>
       </c>
       <c r="D14">
-        <v>23.25832445185754</v>
+        <v>23.35104583060892</v>
       </c>
       <c r="E14">
-        <v>-5.2536</v>
+        <v>-4.981399999999999</v>
       </c>
       <c r="F14">
-        <v>3.2664</v>
+        <v>3.5386</v>
       </c>
       <c r="G14">
         <v>5.26</v>
@@ -2429,28 +2429,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M14">
-        <v>0.16429992</v>
+        <v>0.17799158</v>
       </c>
       <c r="N14">
-        <v>7.509033413333333</v>
+        <v>7.495341753333334</v>
       </c>
       <c r="O14">
-        <v>2.252710024</v>
+        <v>2.248602526</v>
       </c>
       <c r="P14">
-        <v>5.256323389333334</v>
+        <v>5.246739227333334</v>
       </c>
       <c r="Q14">
-        <v>5.916323389333334</v>
+        <v>5.906739227333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1926163928645457</v>
+        <v>0.1938417884266813</v>
       </c>
       <c r="T14">
-        <v>1.023668865357767</v>
+        <v>1.032212865521721</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>46.70320797072412</v>
+        <v>43.11065351143764</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1732196559312127</v>
+        <v>0.1727116861416251</v>
       </c>
       <c r="C15">
-        <v>25.07244583060892</v>
+        <v>24.89370945242219</v>
       </c>
       <c r="D15">
-        <v>23.35104583060892</v>
+        <v>23.44450945242219</v>
       </c>
       <c r="E15">
-        <v>-4.981399999999999</v>
+        <v>-4.709199999999999</v>
       </c>
       <c r="F15">
-        <v>3.5386</v>
+        <v>3.8108</v>
       </c>
       <c r="G15">
         <v>5.26</v>
@@ -2511,28 +2511,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M15">
-        <v>0.17799158</v>
+        <v>0.19168324</v>
       </c>
       <c r="N15">
-        <v>7.495341753333334</v>
+        <v>7.481650093333334</v>
       </c>
       <c r="O15">
-        <v>2.248602526</v>
+        <v>2.244495028</v>
       </c>
       <c r="P15">
-        <v>5.246739227333334</v>
+        <v>5.237155065333334</v>
       </c>
       <c r="Q15">
-        <v>5.906739227333334</v>
+        <v>5.897155065333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1938417884266813</v>
+        <v>0.1950956815600292</v>
       </c>
       <c r="T15">
-        <v>1.032212865521721</v>
+        <v>1.040955563363905</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>43.11065351143764</v>
+        <v>40.03132111776353</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1727116861416251</v>
+        <v>0.1722037163520376</v>
       </c>
       <c r="C16">
-        <v>24.89370945242219</v>
+        <v>24.71572426569843</v>
       </c>
       <c r="D16">
-        <v>23.44450945242219</v>
+        <v>23.53872426569843</v>
       </c>
       <c r="E16">
-        <v>-4.709199999999999</v>
+        <v>-4.436999999999999</v>
       </c>
       <c r="F16">
-        <v>3.8108</v>
+        <v>4.083</v>
       </c>
       <c r="G16">
         <v>5.26</v>
@@ -2593,28 +2593,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M16">
-        <v>0.19168324</v>
+        <v>0.2053749</v>
       </c>
       <c r="N16">
-        <v>7.481650093333334</v>
+        <v>7.467958433333334</v>
       </c>
       <c r="O16">
-        <v>2.244495028</v>
+        <v>2.24038753</v>
       </c>
       <c r="P16">
-        <v>5.237155065333334</v>
+        <v>5.227570903333334</v>
       </c>
       <c r="Q16">
-        <v>5.897155065333334</v>
+        <v>5.887570903333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1950956815600292</v>
+        <v>0.1963790780612207</v>
       </c>
       <c r="T16">
-        <v>1.040955563363905</v>
+        <v>1.049903971743553</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>40.03132111776353</v>
+        <v>37.36256637657929</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1722037163520376</v>
+        <v>0.17169574656245</v>
       </c>
       <c r="C17">
-        <v>24.71572426569843</v>
+        <v>24.5384993632604</v>
       </c>
       <c r="D17">
-        <v>23.53872426569843</v>
+        <v>23.6336993632604</v>
       </c>
       <c r="E17">
-        <v>-4.437</v>
+        <v>-4.1648</v>
       </c>
       <c r="F17">
-        <v>4.082999999999999</v>
+        <v>4.3552</v>
       </c>
       <c r="G17">
         <v>5.26</v>
@@ -2675,28 +2675,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M17">
-        <v>0.2053748999999999</v>
+        <v>0.21906656</v>
       </c>
       <c r="N17">
-        <v>7.467958433333334</v>
+        <v>7.454266773333334</v>
       </c>
       <c r="O17">
-        <v>2.24038753</v>
+        <v>2.236280032</v>
       </c>
       <c r="P17">
-        <v>5.227570903333334</v>
+        <v>5.217986741333334</v>
       </c>
       <c r="Q17">
-        <v>5.887570903333334</v>
+        <v>5.877986741333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1963790780612207</v>
+        <v>0.1976930316219644</v>
       </c>
       <c r="T17">
-        <v>1.049903971743553</v>
+        <v>1.059065437465574</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>37.3625663765793</v>
+        <v>35.02740597804308</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.17169574656245</v>
+        <v>0.1711877767728625</v>
       </c>
       <c r="C18">
-        <v>24.5384993632604</v>
+        <v>24.36204398527789</v>
       </c>
       <c r="D18">
-        <v>23.6336993632604</v>
+        <v>23.72944398527789</v>
       </c>
       <c r="E18">
-        <v>-4.1648</v>
+        <v>-3.8926</v>
       </c>
       <c r="F18">
-        <v>4.3552</v>
+        <v>4.6274</v>
       </c>
       <c r="G18">
         <v>5.26</v>
@@ -2757,28 +2757,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M18">
-        <v>0.21906656</v>
+        <v>0.23275822</v>
       </c>
       <c r="N18">
-        <v>7.454266773333334</v>
+        <v>7.440575113333334</v>
       </c>
       <c r="O18">
-        <v>2.236280032</v>
+        <v>2.232172534</v>
       </c>
       <c r="P18">
-        <v>5.217986741333334</v>
+        <v>5.208402579333334</v>
       </c>
       <c r="Q18">
-        <v>5.877986741333334</v>
+        <v>5.868402579333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1976930316219644</v>
+        <v>0.1990386467142922</v>
       </c>
       <c r="T18">
-        <v>1.059065437465574</v>
+        <v>1.068447661397764</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>35.02740597804308</v>
+        <v>32.96697033227585</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1711877767728625</v>
+        <v>0.1706798069832749</v>
       </c>
       <c r="C19">
-        <v>24.36204398527789</v>
+        <v>24.1863675222645</v>
       </c>
       <c r="D19">
-        <v>23.72944398527789</v>
+        <v>23.8259675222645</v>
       </c>
       <c r="E19">
-        <v>-3.8926</v>
+        <v>-3.620399999999999</v>
       </c>
       <c r="F19">
-        <v>4.6274</v>
+        <v>4.8996</v>
       </c>
       <c r="G19">
         <v>5.26</v>
@@ -2839,28 +2839,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M19">
-        <v>0.23275822</v>
+        <v>0.24644988</v>
       </c>
       <c r="N19">
-        <v>7.440575113333334</v>
+        <v>7.426883453333334</v>
       </c>
       <c r="O19">
-        <v>2.232172534</v>
+        <v>2.228065036</v>
       </c>
       <c r="P19">
-        <v>5.208402579333334</v>
+        <v>5.198818417333333</v>
       </c>
       <c r="Q19">
-        <v>5.868402579333334</v>
+        <v>5.858818417333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1990386467142922</v>
+        <v>0.2004170816869207</v>
       </c>
       <c r="T19">
-        <v>1.068447661397764</v>
+        <v>1.078058720060007</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>32.96697033227585</v>
+        <v>31.13547198048274</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.170679806983275</v>
+        <v>0.1701718371936874</v>
       </c>
       <c r="C20">
-        <v>24.1863675222645</v>
+        <v>24.01147951814792</v>
       </c>
       <c r="D20">
-        <v>23.8259675222645</v>
+        <v>23.92327951814792</v>
       </c>
       <c r="E20">
-        <v>-3.6204</v>
+        <v>-3.348199999999999</v>
       </c>
       <c r="F20">
-        <v>4.8996</v>
+        <v>5.1718</v>
       </c>
       <c r="G20">
         <v>5.26</v>
@@ -2921,28 +2921,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M20">
-        <v>0.24644988</v>
+        <v>0.26014154</v>
       </c>
       <c r="N20">
-        <v>7.426883453333334</v>
+        <v>7.413191793333334</v>
       </c>
       <c r="O20">
-        <v>2.228065036</v>
+        <v>2.223957538</v>
       </c>
       <c r="P20">
-        <v>5.198818417333333</v>
+        <v>5.189234255333334</v>
       </c>
       <c r="Q20">
-        <v>5.858818417333334</v>
+        <v>5.849234255333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2004170816869207</v>
+        <v>0.2018295520909721</v>
       </c>
       <c r="T20">
-        <v>1.078058720060007</v>
+        <v>1.087907088812675</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>31.13547198048274</v>
+        <v>29.49676292887839</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1701718371936874</v>
+        <v>0.1696638674040999</v>
       </c>
       <c r="C21">
-        <v>24.01147951814792</v>
+        <v>23.83738967341564</v>
       </c>
       <c r="D21">
-        <v>23.92327951814792</v>
+        <v>24.02138967341564</v>
       </c>
       <c r="E21">
-        <v>-3.348199999999999</v>
+        <v>-3.076</v>
       </c>
       <c r="F21">
-        <v>5.1718</v>
+        <v>5.444</v>
       </c>
       <c r="G21">
         <v>5.26</v>
@@ -3003,28 +3003,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M21">
-        <v>0.26014154</v>
+        <v>0.2738332</v>
       </c>
       <c r="N21">
-        <v>7.413191793333334</v>
+        <v>7.399500133333333</v>
       </c>
       <c r="O21">
-        <v>2.223957538</v>
+        <v>2.21985004</v>
       </c>
       <c r="P21">
-        <v>5.189234255333334</v>
+        <v>5.179650093333334</v>
       </c>
       <c r="Q21">
-        <v>5.849234255333334</v>
+        <v>5.839650093333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2018295520909721</v>
+        <v>0.2032773342551248</v>
       </c>
       <c r="T21">
-        <v>1.087907088812675</v>
+        <v>1.098001666784161</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>29.49676292887839</v>
+        <v>28.02192478243446</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1696638674040999</v>
+        <v>0.1691558976145123</v>
       </c>
       <c r="C22">
-        <v>23.83738967341564</v>
+        <v>23.66410784833855</v>
       </c>
       <c r="D22">
-        <v>24.02138967341564</v>
+        <v>24.12030784833855</v>
       </c>
       <c r="E22">
-        <v>-3.076</v>
+        <v>-2.803799999999999</v>
       </c>
       <c r="F22">
-        <v>5.444</v>
+        <v>5.716200000000001</v>
       </c>
       <c r="G22">
         <v>5.26</v>
@@ -3085,28 +3085,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M22">
-        <v>0.2738332</v>
+        <v>0.28752486</v>
       </c>
       <c r="N22">
-        <v>7.399500133333333</v>
+        <v>7.385808473333334</v>
       </c>
       <c r="O22">
-        <v>2.21985004</v>
+        <v>2.215742542</v>
       </c>
       <c r="P22">
-        <v>5.179650093333334</v>
+        <v>5.170065931333334</v>
       </c>
       <c r="Q22">
-        <v>5.839650093333334</v>
+        <v>5.830065931333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2032773342551248</v>
+        <v>0.204761769132294</v>
       </c>
       <c r="T22">
-        <v>1.098001666784161</v>
+        <v>1.108351803691634</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>28.02192478243446</v>
+        <v>26.68754741184235</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1691558976145123</v>
+        <v>0.1686479278249247</v>
       </c>
       <c r="C23">
-        <v>23.66410784833856</v>
+        <v>23.49164406627435</v>
       </c>
       <c r="D23">
-        <v>24.12030784833856</v>
+        <v>24.22004406627435</v>
       </c>
       <c r="E23">
-        <v>-2.8038</v>
+        <v>-2.5316</v>
       </c>
       <c r="F23">
-        <v>5.7162</v>
+        <v>5.9884</v>
       </c>
       <c r="G23">
         <v>5.26</v>
@@ -3167,28 +3167,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M23">
-        <v>0.28752486</v>
+        <v>0.30121652</v>
       </c>
       <c r="N23">
-        <v>7.385808473333334</v>
+        <v>7.372116813333334</v>
       </c>
       <c r="O23">
-        <v>2.215742542</v>
+        <v>2.211635044</v>
       </c>
       <c r="P23">
-        <v>5.170065931333334</v>
+        <v>5.160481769333334</v>
       </c>
       <c r="Q23">
-        <v>5.830065931333334</v>
+        <v>5.820481769333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.204761769132294</v>
+        <v>0.2062842664422112</v>
       </c>
       <c r="T23">
-        <v>1.108351803691634</v>
+        <v>1.118967328724939</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>26.68754741184235</v>
+        <v>25.47447707494043</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1686479278249247</v>
+        <v>0.1681399580353372</v>
       </c>
       <c r="C24">
-        <v>23.49164406627435</v>
+        <v>23.32000851705333</v>
       </c>
       <c r="D24">
-        <v>24.22004406627435</v>
+        <v>24.32060851705333</v>
       </c>
       <c r="E24">
-        <v>-2.5316</v>
+        <v>-2.259399999999999</v>
       </c>
       <c r="F24">
-        <v>5.9884</v>
+        <v>6.2606</v>
       </c>
       <c r="G24">
         <v>5.26</v>
@@ -3249,28 +3249,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M24">
-        <v>0.30121652</v>
+        <v>0.31490818</v>
       </c>
       <c r="N24">
-        <v>7.372116813333334</v>
+        <v>7.358425153333334</v>
       </c>
       <c r="O24">
-        <v>2.211635044</v>
+        <v>2.207527546</v>
       </c>
       <c r="P24">
-        <v>5.160481769333334</v>
+        <v>5.150897607333334</v>
       </c>
       <c r="Q24">
-        <v>5.820481769333334</v>
+        <v>5.810897607333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2062842664422112</v>
+        <v>0.2078463091368015</v>
       </c>
       <c r="T24">
-        <v>1.118967328724939</v>
+        <v>1.129858581681187</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>25.47447707494043</v>
+        <v>24.36689111516041</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1681399580353372</v>
+        <v>0.1676319882457496</v>
       </c>
       <c r="C25">
-        <v>23.32000851705333</v>
+        <v>23.14921156044887</v>
       </c>
       <c r="D25">
-        <v>24.32060851705333</v>
+        <v>24.42201156044887</v>
       </c>
       <c r="E25">
-        <v>-2.259399999999999</v>
+        <v>-1.9872</v>
       </c>
       <c r="F25">
-        <v>6.2606</v>
+        <v>6.5328</v>
       </c>
       <c r="G25">
         <v>5.26</v>
@@ -3331,28 +3331,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M25">
-        <v>0.31490818</v>
+        <v>0.32859984</v>
       </c>
       <c r="N25">
-        <v>7.358425153333334</v>
+        <v>7.344733493333334</v>
       </c>
       <c r="O25">
-        <v>2.207527546</v>
+        <v>2.203420048</v>
       </c>
       <c r="P25">
-        <v>5.150897607333334</v>
+        <v>5.141313445333334</v>
       </c>
       <c r="Q25">
-        <v>5.810897607333334</v>
+        <v>5.801313445333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2078463091368015</v>
+        <v>0.2094494582180916</v>
       </c>
       <c r="T25">
-        <v>1.129858581681187</v>
+        <v>1.141036446557337</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>24.36689111516041</v>
+        <v>23.35160398536206</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1676319882457496</v>
+        <v>0.1671240184561621</v>
       </c>
       <c r="C26">
-        <v>23.14921156044887</v>
+        <v>22.9792637297351</v>
       </c>
       <c r="D26">
-        <v>24.42201156044887</v>
+        <v>24.5242637297351</v>
       </c>
       <c r="E26">
-        <v>-1.987200000000001</v>
+        <v>-1.715</v>
       </c>
       <c r="F26">
-        <v>6.532799999999999</v>
+        <v>6.805</v>
       </c>
       <c r="G26">
         <v>5.26</v>
@@ -3413,28 +3413,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M26">
-        <v>0.3285998399999999</v>
+        <v>0.3422915</v>
       </c>
       <c r="N26">
-        <v>7.344733493333334</v>
+        <v>7.331041833333334</v>
       </c>
       <c r="O26">
-        <v>2.203420048</v>
+        <v>2.19931255</v>
       </c>
       <c r="P26">
-        <v>5.141313445333334</v>
+        <v>5.131729283333334</v>
       </c>
       <c r="Q26">
-        <v>5.801313445333334</v>
+        <v>5.791729283333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2094494582180916</v>
+        <v>0.2110953579415495</v>
       </c>
       <c r="T26">
-        <v>1.141036446557337</v>
+        <v>1.152512387830184</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>23.35160398536206</v>
+        <v>22.41753982594757</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1671240184561621</v>
+        <v>0.1666160486665745</v>
       </c>
       <c r="C27">
-        <v>22.9792637297351</v>
+        <v>22.81017573533433</v>
       </c>
       <c r="D27">
-        <v>24.5242637297351</v>
+        <v>24.62737573533433</v>
       </c>
       <c r="E27">
-        <v>-1.715</v>
+        <v>-1.442799999999999</v>
       </c>
       <c r="F27">
-        <v>6.805</v>
+        <v>7.0772</v>
       </c>
       <c r="G27">
         <v>5.26</v>
@@ -3495,28 +3495,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M27">
-        <v>0.3422915</v>
+        <v>0.35598316</v>
       </c>
       <c r="N27">
-        <v>7.331041833333334</v>
+        <v>7.317350173333334</v>
       </c>
       <c r="O27">
-        <v>2.19931255</v>
+        <v>2.195205052</v>
       </c>
       <c r="P27">
-        <v>5.131729283333334</v>
+        <v>5.122145121333334</v>
       </c>
       <c r="Q27">
-        <v>5.791729283333334</v>
+        <v>5.782145121333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2110953579415495</v>
+        <v>0.2127857414413169</v>
       </c>
       <c r="T27">
-        <v>1.152512387830184</v>
+        <v>1.164298489677972</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>22.41753982594757</v>
+        <v>21.55532675571882</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1666160486665745</v>
+        <v>0.166108078876987</v>
       </c>
       <c r="C28">
-        <v>22.81017573533433</v>
+        <v>22.64195846855678</v>
       </c>
       <c r="D28">
-        <v>24.62737573533433</v>
+        <v>24.73135846855677</v>
       </c>
       <c r="E28">
-        <v>-1.442799999999999</v>
+        <v>-1.170599999999999</v>
       </c>
       <c r="F28">
-        <v>7.0772</v>
+        <v>7.3494</v>
       </c>
       <c r="G28">
         <v>5.26</v>
@@ -3577,28 +3577,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M28">
-        <v>0.35598316</v>
+        <v>0.36967482</v>
       </c>
       <c r="N28">
-        <v>7.317350173333334</v>
+        <v>7.303658513333334</v>
       </c>
       <c r="O28">
-        <v>2.195205052</v>
+        <v>2.191097554</v>
       </c>
       <c r="P28">
-        <v>5.122145121333334</v>
+        <v>5.112560959333333</v>
       </c>
       <c r="Q28">
-        <v>5.782145121333334</v>
+        <v>5.772560959333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2127857414413169</v>
+        <v>0.2145224368177904</v>
       </c>
       <c r="T28">
-        <v>1.164298489677972</v>
+        <v>1.1764074984257</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>21.55532675571882</v>
+        <v>20.75698132032183</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.166108078876987</v>
+        <v>0.1656001090873994</v>
       </c>
       <c r="C29">
-        <v>22.64195846855678</v>
+        <v>22.47462300543563</v>
       </c>
       <c r="D29">
-        <v>24.73135846855677</v>
+        <v>24.83622300543563</v>
       </c>
       <c r="E29">
-        <v>-1.170599999999999</v>
+        <v>-0.8983999999999988</v>
       </c>
       <c r="F29">
-        <v>7.3494</v>
+        <v>7.621600000000001</v>
       </c>
       <c r="G29">
         <v>5.26</v>
@@ -3659,28 +3659,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M29">
-        <v>0.36967482</v>
+        <v>0.38336648</v>
       </c>
       <c r="N29">
-        <v>7.303658513333334</v>
+        <v>7.289966853333333</v>
       </c>
       <c r="O29">
-        <v>2.191097554</v>
+        <v>2.186990056</v>
       </c>
       <c r="P29">
-        <v>5.112560959333333</v>
+        <v>5.102976797333334</v>
       </c>
       <c r="Q29">
-        <v>5.772560959333333</v>
+        <v>5.762976797333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2145224368177904</v>
+        <v>0.2163073737324992</v>
       </c>
       <c r="T29">
-        <v>1.1764074984257</v>
+        <v>1.188852868527531</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>20.75698132032183</v>
+        <v>20.01566055888176</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1656001090873994</v>
+        <v>0.1650921392978118</v>
       </c>
       <c r="C30">
-        <v>22.47462300543563</v>
+        <v>22.30818061065995</v>
       </c>
       <c r="D30">
-        <v>24.83622300543563</v>
+        <v>24.94198061065995</v>
       </c>
       <c r="E30">
-        <v>-0.8983999999999988</v>
+        <v>-0.626199999999999</v>
       </c>
       <c r="F30">
-        <v>7.621600000000001</v>
+        <v>7.893800000000001</v>
       </c>
       <c r="G30">
         <v>5.26</v>
@@ -3741,28 +3741,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M30">
-        <v>0.38336648</v>
+        <v>0.39705814</v>
       </c>
       <c r="N30">
-        <v>7.289966853333333</v>
+        <v>7.276275193333333</v>
       </c>
       <c r="O30">
-        <v>2.186990056</v>
+        <v>2.182882558</v>
       </c>
       <c r="P30">
-        <v>5.102976797333334</v>
+        <v>5.093392635333334</v>
       </c>
       <c r="Q30">
-        <v>5.762976797333334</v>
+        <v>5.753392635333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2163073737324992</v>
+        <v>0.2181425905602984</v>
       </c>
       <c r="T30">
-        <v>1.188852868527531</v>
+        <v>1.201648812435048</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>20.01566055888176</v>
+        <v>19.32546536719618</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1650921392978118</v>
+        <v>0.1645841695082243</v>
       </c>
       <c r="C31">
-        <v>22.30818061065995</v>
+        <v>22.14264274160844</v>
       </c>
       <c r="D31">
-        <v>24.94198061065995</v>
+        <v>25.04864274160844</v>
       </c>
       <c r="E31">
-        <v>-0.6262000000000008</v>
+        <v>-0.354000000000001</v>
       </c>
       <c r="F31">
-        <v>7.893799999999999</v>
+        <v>8.165999999999999</v>
       </c>
       <c r="G31">
         <v>5.26</v>
@@ -3823,28 +3823,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M31">
-        <v>0.3970581399999999</v>
+        <v>0.4107497999999999</v>
       </c>
       <c r="N31">
-        <v>7.276275193333333</v>
+        <v>7.262583533333334</v>
       </c>
       <c r="O31">
-        <v>2.182882558</v>
+        <v>2.17877506</v>
       </c>
       <c r="P31">
-        <v>5.093392635333334</v>
+        <v>5.083808473333335</v>
       </c>
       <c r="Q31">
-        <v>5.753392635333334</v>
+        <v>5.743808473333335</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2181425905602984</v>
+        <v>0.2200302421546061</v>
       </c>
       <c r="T31">
-        <v>1.201648812435048</v>
+        <v>1.214810354739923</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>19.32546536719618</v>
+        <v>18.68128318828965</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1645841695082243</v>
+        <v>0.1640761997186367</v>
       </c>
       <c r="C32">
-        <v>22.14264274160844</v>
+        <v>21.97802105248735</v>
       </c>
       <c r="D32">
-        <v>25.04864274160844</v>
+        <v>25.15622105248735</v>
       </c>
       <c r="E32">
-        <v>-0.354000000000001</v>
+        <v>-0.08179999999999943</v>
       </c>
       <c r="F32">
-        <v>8.165999999999999</v>
+        <v>8.4382</v>
       </c>
       <c r="G32">
         <v>5.26</v>
@@ -3905,28 +3905,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M32">
-        <v>0.4107497999999999</v>
+        <v>0.42444146</v>
       </c>
       <c r="N32">
-        <v>7.262583533333334</v>
+        <v>7.248891873333334</v>
       </c>
       <c r="O32">
-        <v>2.17877506</v>
+        <v>2.174667562</v>
       </c>
       <c r="P32">
-        <v>5.083808473333335</v>
+        <v>5.074224311333333</v>
       </c>
       <c r="Q32">
-        <v>5.743808473333335</v>
+        <v>5.734224311333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2200302421546061</v>
+        <v>0.2219726082878793</v>
       </c>
       <c r="T32">
-        <v>1.214810354739923</v>
+        <v>1.228353391024649</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>18.68128318828965</v>
+        <v>18.07866114995772</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1640761997186367</v>
+        <v>0.1635682299290492</v>
       </c>
       <c r="C33">
-        <v>21.97802105248735</v>
+        <v>21.81432739857533</v>
       </c>
       <c r="D33">
-        <v>25.15622105248735</v>
+        <v>25.26472739857533</v>
       </c>
       <c r="E33">
-        <v>-0.08179999999999943</v>
+        <v>0.1904000000000003</v>
       </c>
       <c r="F33">
-        <v>8.4382</v>
+        <v>8.7104</v>
       </c>
       <c r="G33">
         <v>5.26</v>
@@ -3987,28 +3987,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M33">
-        <v>0.42444146</v>
+        <v>0.43813312</v>
       </c>
       <c r="N33">
-        <v>7.248891873333334</v>
+        <v>7.235200213333334</v>
       </c>
       <c r="O33">
-        <v>2.174667562</v>
+        <v>2.170560064</v>
       </c>
       <c r="P33">
-        <v>5.074224311333333</v>
+        <v>5.064640149333334</v>
       </c>
       <c r="Q33">
-        <v>5.734224311333334</v>
+        <v>5.724640149333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2219726082878793</v>
+        <v>0.2239721028368371</v>
       </c>
       <c r="T33">
-        <v>1.228353391024649</v>
+        <v>1.242294751905985</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>18.07866114995772</v>
+        <v>17.51370298902154</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1635682299290492</v>
+        <v>0.1630602601394616</v>
       </c>
       <c r="C34">
-        <v>21.81432739857533</v>
+        <v>21.65157384057859</v>
       </c>
       <c r="D34">
-        <v>25.26472739857533</v>
+        <v>25.37417384057859</v>
       </c>
       <c r="E34">
-        <v>0.1904000000000003</v>
+        <v>0.4626000000000001</v>
       </c>
       <c r="F34">
-        <v>8.7104</v>
+        <v>8.9826</v>
       </c>
       <c r="G34">
         <v>5.26</v>
@@ -4069,28 +4069,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M34">
-        <v>0.43813312</v>
+        <v>0.45182478</v>
       </c>
       <c r="N34">
-        <v>7.235200213333334</v>
+        <v>7.221508553333334</v>
       </c>
       <c r="O34">
-        <v>2.170560064</v>
+        <v>2.166452566</v>
       </c>
       <c r="P34">
-        <v>5.064640149333334</v>
+        <v>5.055055987333334</v>
       </c>
       <c r="Q34">
-        <v>5.724640149333334</v>
+        <v>5.715055987333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2239721028368371</v>
+        <v>0.2260312837902413</v>
       </c>
       <c r="T34">
-        <v>1.242294751905985</v>
+        <v>1.256652272813629</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>17.51370298902154</v>
+        <v>16.98298471662695</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1630602601394616</v>
+        <v>0.1625522903498741</v>
       </c>
       <c r="C35">
-        <v>21.65157384057859</v>
+        <v>21.48977264909988</v>
       </c>
       <c r="D35">
-        <v>25.37417384057859</v>
+        <v>25.48457264909988</v>
       </c>
       <c r="E35">
-        <v>0.4626000000000001</v>
+        <v>0.7347999999999999</v>
       </c>
       <c r="F35">
-        <v>8.9826</v>
+        <v>9.254799999999999</v>
       </c>
       <c r="G35">
         <v>5.26</v>
@@ -4151,28 +4151,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M35">
-        <v>0.45182478</v>
+        <v>0.46551644</v>
       </c>
       <c r="N35">
-        <v>7.221508553333334</v>
+        <v>7.207816893333334</v>
       </c>
       <c r="O35">
-        <v>2.166452566</v>
+        <v>2.162345068</v>
       </c>
       <c r="P35">
-        <v>5.055055987333334</v>
+        <v>5.045471825333333</v>
       </c>
       <c r="Q35">
-        <v>5.715055987333334</v>
+        <v>5.705471825333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2260312837902413</v>
+        <v>0.2281528641664759</v>
       </c>
       <c r="T35">
-        <v>1.256652272813629</v>
+        <v>1.271444870112413</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>16.98298471662695</v>
+        <v>16.48348516613792</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1625522903498741</v>
+        <v>0.1620443205602865</v>
       </c>
       <c r="C36">
-        <v>21.48977264909988</v>
+        <v>21.32893630922449</v>
       </c>
       <c r="D36">
-        <v>25.48457264909988</v>
+        <v>25.59593630922449</v>
       </c>
       <c r="E36">
-        <v>0.7347999999999999</v>
+        <v>1.007000000000001</v>
       </c>
       <c r="F36">
-        <v>9.254799999999999</v>
+        <v>9.527000000000001</v>
       </c>
       <c r="G36">
         <v>5.26</v>
@@ -4233,28 +4233,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M36">
-        <v>0.46551644</v>
+        <v>0.4792081</v>
       </c>
       <c r="N36">
-        <v>7.207816893333334</v>
+        <v>7.194125233333334</v>
       </c>
       <c r="O36">
-        <v>2.162345068</v>
+        <v>2.15823757</v>
       </c>
       <c r="P36">
-        <v>5.045471825333333</v>
+        <v>5.035887663333334</v>
       </c>
       <c r="Q36">
-        <v>5.705471825333333</v>
+        <v>5.695887663333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2281528641664759</v>
+        <v>0.2303397239389024</v>
       </c>
       <c r="T36">
-        <v>1.271444870112413</v>
+        <v>1.286692624251161</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>16.48348516613792</v>
+        <v>16.01252844710541</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1620443205602865</v>
+        <v>0.161536350770699</v>
       </c>
       <c r="C37">
-        <v>21.32893630922449</v>
+        <v>21.16907752522716</v>
       </c>
       <c r="D37">
-        <v>25.59593630922449</v>
+        <v>25.70827752522716</v>
       </c>
       <c r="E37">
-        <v>1.007000000000001</v>
+        <v>1.279200000000001</v>
       </c>
       <c r="F37">
-        <v>9.527000000000001</v>
+        <v>9.799200000000001</v>
       </c>
       <c r="G37">
         <v>5.26</v>
@@ -4315,28 +4315,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M37">
-        <v>0.4792081</v>
+        <v>0.49289976</v>
       </c>
       <c r="N37">
-        <v>7.194125233333334</v>
+        <v>7.180433573333334</v>
       </c>
       <c r="O37">
-        <v>2.15823757</v>
+        <v>2.154130072</v>
       </c>
       <c r="P37">
-        <v>5.035887663333334</v>
+        <v>5.026303501333333</v>
       </c>
       <c r="Q37">
-        <v>5.695887663333334</v>
+        <v>5.686303501333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2303397239389024</v>
+        <v>0.2325949230792172</v>
       </c>
       <c r="T37">
-        <v>1.286692624251161</v>
+        <v>1.302416870706745</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>16.01252844710541</v>
+        <v>15.56773599024137</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.161536350770699</v>
+        <v>0.1610283809811114</v>
       </c>
       <c r="C38">
-        <v>21.16907752522716</v>
+        <v>21.01020922540344</v>
       </c>
       <c r="D38">
-        <v>25.70827752522716</v>
+        <v>25.82160922540343</v>
       </c>
       <c r="E38">
-        <v>1.279199999999999</v>
+        <v>1.551399999999999</v>
       </c>
       <c r="F38">
-        <v>9.799199999999999</v>
+        <v>10.0714</v>
       </c>
       <c r="G38">
         <v>5.26</v>
@@ -4397,28 +4397,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M38">
-        <v>0.4928997599999999</v>
+        <v>0.5065914199999999</v>
       </c>
       <c r="N38">
-        <v>7.180433573333334</v>
+        <v>7.166741913333334</v>
       </c>
       <c r="O38">
-        <v>2.154130072</v>
+        <v>2.150022574</v>
       </c>
       <c r="P38">
-        <v>5.026303501333333</v>
+        <v>5.016719339333334</v>
       </c>
       <c r="Q38">
-        <v>5.686303501333334</v>
+        <v>5.676719339333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2325949230792172</v>
+        <v>0.234921715843034</v>
       </c>
       <c r="T38">
-        <v>1.302416870706745</v>
+        <v>1.318640299589489</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>15.56773599024137</v>
+        <v>15.1469863688835</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1610283809811114</v>
+        <v>0.1605204111915239</v>
       </c>
       <c r="C39">
-        <v>21.01020922540344</v>
+        <v>20.85234456702928</v>
       </c>
       <c r="D39">
-        <v>25.82160922540343</v>
+        <v>25.93594456702928</v>
       </c>
       <c r="E39">
-        <v>1.551399999999999</v>
+        <v>1.823600000000001</v>
       </c>
       <c r="F39">
-        <v>10.0714</v>
+        <v>10.3436</v>
       </c>
       <c r="G39">
         <v>5.26</v>
@@ -4479,28 +4479,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M39">
-        <v>0.5065914199999999</v>
+        <v>0.52028308</v>
       </c>
       <c r="N39">
-        <v>7.166741913333334</v>
+        <v>7.153050253333333</v>
       </c>
       <c r="O39">
-        <v>2.150022574</v>
+        <v>2.145915076</v>
       </c>
       <c r="P39">
-        <v>5.016719339333334</v>
+        <v>5.007135177333334</v>
       </c>
       <c r="Q39">
-        <v>5.676719339333334</v>
+        <v>5.667135177333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.234921715843034</v>
+        <v>0.2373235664379418</v>
       </c>
       <c r="T39">
-        <v>1.318640299589489</v>
+        <v>1.335387064887806</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>15.1469863688835</v>
+        <v>14.74838146443919</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1605204111915239</v>
+        <v>0.1600124414019363</v>
       </c>
       <c r="C40">
-        <v>20.85234456702928</v>
+        <v>20.69549694145321</v>
       </c>
       <c r="D40">
-        <v>25.93594456702928</v>
+        <v>26.05129694145322</v>
       </c>
       <c r="E40">
-        <v>1.823600000000001</v>
+        <v>2.095800000000001</v>
       </c>
       <c r="F40">
-        <v>10.3436</v>
+        <v>10.6158</v>
       </c>
       <c r="G40">
         <v>5.26</v>
@@ -4561,28 +4561,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M40">
-        <v>0.52028308</v>
+        <v>0.53397474</v>
       </c>
       <c r="N40">
-        <v>7.153050253333333</v>
+        <v>7.139358593333334</v>
       </c>
       <c r="O40">
-        <v>2.145915076</v>
+        <v>2.141807578</v>
       </c>
       <c r="P40">
-        <v>5.007135177333334</v>
+        <v>4.997551015333334</v>
       </c>
       <c r="Q40">
-        <v>5.667135177333334</v>
+        <v>5.657551015333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2373235664379418</v>
+        <v>0.2398041662326825</v>
       </c>
       <c r="T40">
-        <v>1.335387064887806</v>
+        <v>1.352682904458199</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>14.74838146443919</v>
+        <v>14.37021783714588</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1600124414019363</v>
+        <v>0.1595044716123488</v>
       </c>
       <c r="C41">
-        <v>20.69549694145321</v>
+        <v>20.53967997932484</v>
       </c>
       <c r="D41">
-        <v>26.05129694145322</v>
+        <v>26.16767997932484</v>
       </c>
       <c r="E41">
-        <v>2.095800000000001</v>
+        <v>2.368</v>
       </c>
       <c r="F41">
-        <v>10.6158</v>
+        <v>10.888</v>
       </c>
       <c r="G41">
         <v>5.26</v>
@@ -4643,28 +4643,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M41">
-        <v>0.53397474</v>
+        <v>0.5476664</v>
       </c>
       <c r="N41">
-        <v>7.139358593333334</v>
+        <v>7.125666933333334</v>
       </c>
       <c r="O41">
-        <v>2.141807578</v>
+        <v>2.13770008</v>
       </c>
       <c r="P41">
-        <v>4.997551015333334</v>
+        <v>4.987966853333334</v>
       </c>
       <c r="Q41">
-        <v>5.657551015333334</v>
+        <v>5.647966853333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2398041662326825</v>
+        <v>0.242367452687248</v>
       </c>
       <c r="T41">
-        <v>1.352682904458199</v>
+        <v>1.370555272014272</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>14.37021783714588</v>
+        <v>14.01096239121723</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1595044716123488</v>
+        <v>0.1589965018227612</v>
       </c>
       <c r="C42">
-        <v>20.53967997932484</v>
+        <v>20.38490755596412</v>
       </c>
       <c r="D42">
-        <v>26.16767997932484</v>
+        <v>26.28510755596412</v>
       </c>
       <c r="E42">
-        <v>2.368</v>
+        <v>2.6402</v>
       </c>
       <c r="F42">
-        <v>10.888</v>
+        <v>11.1602</v>
       </c>
       <c r="G42">
         <v>5.26</v>
@@ -4725,28 +4725,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M42">
-        <v>0.5476664</v>
+        <v>0.56135806</v>
       </c>
       <c r="N42">
-        <v>7.125666933333334</v>
+        <v>7.111975273333334</v>
       </c>
       <c r="O42">
-        <v>2.13770008</v>
+        <v>2.133592582</v>
       </c>
       <c r="P42">
-        <v>4.987966853333334</v>
+        <v>4.978382691333334</v>
       </c>
       <c r="Q42">
-        <v>5.647966853333334</v>
+        <v>5.638382691333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.242367452687248</v>
+        <v>0.2450176302080699</v>
       </c>
       <c r="T42">
-        <v>1.370555272014272</v>
+        <v>1.389033482538347</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>14.01096239121723</v>
+        <v>13.66923160118755</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1589965018227612</v>
+        <v>0.1584885320331737</v>
       </c>
       <c r="C43">
-        <v>20.38490755596412</v>
+        <v>20.23119379687601</v>
       </c>
       <c r="D43">
-        <v>26.28510755596412</v>
+        <v>26.40359379687602</v>
       </c>
       <c r="E43">
-        <v>2.6402</v>
+        <v>2.912400000000002</v>
       </c>
       <c r="F43">
-        <v>11.1602</v>
+        <v>11.4324</v>
       </c>
       <c r="G43">
         <v>5.26</v>
@@ -4807,28 +4807,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M43">
-        <v>0.56135806</v>
+        <v>0.57504972</v>
       </c>
       <c r="N43">
-        <v>7.111975273333334</v>
+        <v>7.098283613333334</v>
       </c>
       <c r="O43">
-        <v>2.133592582</v>
+        <v>2.129485084</v>
       </c>
       <c r="P43">
-        <v>4.978382691333334</v>
+        <v>4.968798529333334</v>
       </c>
       <c r="Q43">
-        <v>5.638382691333334</v>
+        <v>5.628798529333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2450176302080699</v>
+        <v>0.2477591931606443</v>
       </c>
       <c r="T43">
-        <v>1.389033482538347</v>
+        <v>1.408148872735667</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>13.66923160118755</v>
+        <v>13.34377370592117</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1584885320331737</v>
+        <v>0.1579805622435861</v>
       </c>
       <c r="C44">
-        <v>20.23119379687601</v>
+        <v>20.07855308341473</v>
       </c>
       <c r="D44">
-        <v>26.40359379687601</v>
+        <v>26.52315308341472</v>
       </c>
       <c r="E44">
-        <v>2.9124</v>
+        <v>3.1846</v>
       </c>
       <c r="F44">
-        <v>11.4324</v>
+        <v>11.7046</v>
       </c>
       <c r="G44">
         <v>5.26</v>
@@ -4889,28 +4889,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M44">
-        <v>0.57504972</v>
+        <v>0.58874138</v>
       </c>
       <c r="N44">
-        <v>7.098283613333334</v>
+        <v>7.084591953333334</v>
       </c>
       <c r="O44">
-        <v>2.129485084</v>
+        <v>2.125377586</v>
       </c>
       <c r="P44">
-        <v>4.968798529333334</v>
+        <v>4.959214367333334</v>
       </c>
       <c r="Q44">
-        <v>5.628798529333334</v>
+        <v>5.619214367333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2477591931606443</v>
+        <v>0.250596951304537</v>
       </c>
       <c r="T44">
-        <v>1.408148872735667</v>
+        <v>1.427934978378506</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>13.34377370592117</v>
+        <v>13.03345338717882</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1579805622435861</v>
+        <v>0.1579345924539985</v>
       </c>
       <c r="C45">
-        <v>20.07855308341473</v>
+        <v>19.81722630049931</v>
       </c>
       <c r="D45">
-        <v>26.52315308341472</v>
+        <v>26.5340263004993</v>
       </c>
       <c r="E45">
-        <v>3.1846</v>
+        <v>3.456799999999999</v>
       </c>
       <c r="F45">
-        <v>11.7046</v>
+        <v>11.9768</v>
       </c>
       <c r="G45">
         <v>5.26</v>
@@ -4971,45 +4971,45 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M45">
-        <v>0.58874138</v>
+        <v>0.62039824</v>
       </c>
       <c r="N45">
-        <v>7.084591953333334</v>
+        <v>7.052935093333334</v>
       </c>
       <c r="O45">
-        <v>2.125377586</v>
+        <v>2.115880528</v>
       </c>
       <c r="P45">
-        <v>4.959214367333334</v>
+        <v>4.937054565333334</v>
       </c>
       <c r="Q45">
-        <v>5.619214367333334</v>
+        <v>5.597054565333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.250596951304537</v>
+        <v>0.2535360579535688</v>
       </c>
       <c r="T45">
-        <v>1.427934978378506</v>
+        <v>1.448427730651446</v>
       </c>
       <c r="U45">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y45">
-        <v>13.03345338717882</v>
+        <v>12.36839958368246</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1579345924539985</v>
+        <v>0.157437122664411</v>
       </c>
       <c r="C46">
-        <v>19.81722630049931</v>
+        <v>19.66326543247961</v>
       </c>
       <c r="D46">
-        <v>26.5340263004993</v>
+        <v>26.65226543247961</v>
       </c>
       <c r="E46">
-        <v>3.456799999999999</v>
+        <v>3.729000000000001</v>
       </c>
       <c r="F46">
-        <v>11.9768</v>
+        <v>12.249</v>
       </c>
       <c r="G46">
         <v>5.26</v>
@@ -5053,28 +5053,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M46">
-        <v>0.62039824</v>
+        <v>0.6344982</v>
       </c>
       <c r="N46">
-        <v>7.052935093333334</v>
+        <v>7.038835133333333</v>
       </c>
       <c r="O46">
-        <v>2.115880528</v>
+        <v>2.11165054</v>
       </c>
       <c r="P46">
-        <v>4.937054565333334</v>
+        <v>4.927184593333333</v>
       </c>
       <c r="Q46">
-        <v>5.597054565333334</v>
+        <v>5.587184593333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2535360579535688</v>
+        <v>0.25658204120802</v>
       </c>
       <c r="T46">
-        <v>1.448427730651446</v>
+        <v>1.469665673916131</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>12.36839958368246</v>
+        <v>12.09354625960063</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.157437122664411</v>
+        <v>0.1569396528748234</v>
       </c>
       <c r="C47">
-        <v>19.66326543247961</v>
+        <v>19.51036305968798</v>
       </c>
       <c r="D47">
-        <v>26.65226543247961</v>
+        <v>26.77156305968798</v>
       </c>
       <c r="E47">
-        <v>3.729000000000001</v>
+        <v>4.001200000000001</v>
       </c>
       <c r="F47">
-        <v>12.249</v>
+        <v>12.5212</v>
       </c>
       <c r="G47">
         <v>5.26</v>
@@ -5135,28 +5135,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M47">
-        <v>0.6344982</v>
+        <v>0.64859816</v>
       </c>
       <c r="N47">
-        <v>7.038835133333333</v>
+        <v>7.024735173333334</v>
       </c>
       <c r="O47">
-        <v>2.11165054</v>
+        <v>2.107420552</v>
       </c>
       <c r="P47">
-        <v>4.927184593333333</v>
+        <v>4.917314621333334</v>
       </c>
       <c r="Q47">
-        <v>5.587184593333333</v>
+        <v>5.577314621333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.25658204120802</v>
+        <v>0.2597408386570805</v>
       </c>
       <c r="T47">
-        <v>1.469665673916131</v>
+        <v>1.491690207672099</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>12.09354625960063</v>
+        <v>11.8306430800441</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1569396528748234</v>
+        <v>0.1564421830852359</v>
       </c>
       <c r="C48">
-        <v>19.51036305968798</v>
+        <v>19.35853345975477</v>
       </c>
       <c r="D48">
-        <v>26.77156305968798</v>
+        <v>26.89193345975477</v>
       </c>
       <c r="E48">
-        <v>4.001200000000001</v>
+        <v>4.273400000000001</v>
       </c>
       <c r="F48">
-        <v>12.5212</v>
+        <v>12.7934</v>
       </c>
       <c r="G48">
         <v>5.26</v>
@@ -5217,28 +5217,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M48">
-        <v>0.64859816</v>
+        <v>0.6626981199999999</v>
       </c>
       <c r="N48">
-        <v>7.024735173333334</v>
+        <v>7.010635213333334</v>
       </c>
       <c r="O48">
-        <v>2.107420552</v>
+        <v>2.103190564</v>
       </c>
       <c r="P48">
-        <v>4.917314621333334</v>
+        <v>4.907444649333334</v>
       </c>
       <c r="Q48">
-        <v>5.577314621333334</v>
+        <v>5.567444649333334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2597408386570805</v>
+        <v>0.2630188360098791</v>
       </c>
       <c r="T48">
-        <v>1.491690207672099</v>
+        <v>1.514545855909425</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.8306430800441</v>
+        <v>11.57892726983039</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1564421830852359</v>
+        <v>0.1559447132956483</v>
       </c>
       <c r="C49">
-        <v>19.35853345975477</v>
+        <v>19.20779116825067</v>
       </c>
       <c r="D49">
-        <v>26.89193345975477</v>
+        <v>27.01339116825067</v>
       </c>
       <c r="E49">
-        <v>4.273400000000001</v>
+        <v>4.5456</v>
       </c>
       <c r="F49">
-        <v>12.7934</v>
+        <v>13.0656</v>
       </c>
       <c r="G49">
         <v>5.26</v>
@@ -5299,28 +5299,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M49">
-        <v>0.6626981199999999</v>
+        <v>0.67679808</v>
       </c>
       <c r="N49">
-        <v>7.010635213333334</v>
+        <v>6.996535253333334</v>
       </c>
       <c r="O49">
-        <v>2.103190564</v>
+        <v>2.098960576</v>
       </c>
       <c r="P49">
-        <v>4.907444649333334</v>
+        <v>4.897574677333333</v>
       </c>
       <c r="Q49">
-        <v>5.567444649333334</v>
+        <v>5.557574677333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2630188360098791</v>
+        <v>0.2664229101839391</v>
       </c>
       <c r="T49">
-        <v>1.514545855909425</v>
+        <v>1.538280567540494</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>11.57892726983039</v>
+        <v>11.33769961837559</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1559447132956483</v>
+        <v>0.1554472435060608</v>
       </c>
       <c r="C50">
-        <v>19.20779116825067</v>
+        <v>19.058150984538</v>
       </c>
       <c r="D50">
-        <v>27.01339116825067</v>
+        <v>27.13595098453801</v>
       </c>
       <c r="E50">
-        <v>4.545599999999999</v>
+        <v>4.8178</v>
       </c>
       <c r="F50">
-        <v>13.0656</v>
+        <v>13.3378</v>
       </c>
       <c r="G50">
         <v>5.26</v>
@@ -5381,28 +5381,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M50">
-        <v>0.6767980799999999</v>
+        <v>0.69089804</v>
       </c>
       <c r="N50">
-        <v>6.996535253333334</v>
+        <v>6.982435293333333</v>
       </c>
       <c r="O50">
-        <v>2.098960576</v>
+        <v>2.094730588</v>
       </c>
       <c r="P50">
-        <v>4.897574677333333</v>
+        <v>4.887704705333333</v>
       </c>
       <c r="Q50">
-        <v>5.557574677333333</v>
+        <v>5.547704705333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2664229101839391</v>
+        <v>0.2699604774628643</v>
       </c>
       <c r="T50">
-        <v>1.538280567540494</v>
+        <v>1.562946052176703</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>11.33769961837559</v>
+        <v>11.10631799351078</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1554472435060608</v>
+        <v>0.1549497737164733</v>
       </c>
       <c r="C51">
-        <v>19.058150984538</v>
+        <v>18.90962797778218</v>
       </c>
       <c r="D51">
-        <v>27.13595098453801</v>
+        <v>27.25962797778218</v>
       </c>
       <c r="E51">
-        <v>4.8178</v>
+        <v>5.09</v>
       </c>
       <c r="F51">
-        <v>13.3378</v>
+        <v>13.61</v>
       </c>
       <c r="G51">
         <v>5.26</v>
@@ -5463,28 +5463,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M51">
-        <v>0.69089804</v>
+        <v>0.7049979999999999</v>
       </c>
       <c r="N51">
-        <v>6.982435293333333</v>
+        <v>6.968335333333334</v>
       </c>
       <c r="O51">
-        <v>2.094730588</v>
+        <v>2.0905006</v>
       </c>
       <c r="P51">
-        <v>4.887704705333333</v>
+        <v>4.877834733333334</v>
       </c>
       <c r="Q51">
-        <v>5.547704705333333</v>
+        <v>5.537834733333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2699604774628643</v>
+        <v>0.2736395474329465</v>
       </c>
       <c r="T51">
-        <v>1.562946052176703</v>
+        <v>1.588598156198361</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>11.10631799351078</v>
+        <v>10.88419163364057</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1549497737164733</v>
+        <v>0.1544523039268857</v>
       </c>
       <c r="C52">
-        <v>18.90962797778218</v>
+        <v>18.7622374931282</v>
       </c>
       <c r="D52">
-        <v>27.25962797778218</v>
+        <v>27.3844374931282</v>
       </c>
       <c r="E52">
-        <v>5.09</v>
+        <v>5.3622</v>
       </c>
       <c r="F52">
-        <v>13.61</v>
+        <v>13.8822</v>
       </c>
       <c r="G52">
         <v>5.26</v>
@@ -5545,28 +5545,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M52">
-        <v>0.7049979999999999</v>
+        <v>0.7190979599999999</v>
       </c>
       <c r="N52">
-        <v>6.968335333333334</v>
+        <v>6.954235373333334</v>
       </c>
       <c r="O52">
-        <v>2.0905006</v>
+        <v>2.086270612</v>
       </c>
       <c r="P52">
-        <v>4.877834733333334</v>
+        <v>4.867964761333334</v>
       </c>
       <c r="Q52">
-        <v>5.537834733333334</v>
+        <v>5.527964761333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2736395474329465</v>
+        <v>0.2774687835242565</v>
       </c>
       <c r="T52">
-        <v>1.588598156198361</v>
+        <v>1.615297284873964</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.88419163364057</v>
+        <v>10.67077611141232</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1544523039268857</v>
+        <v>0.1539548341372981</v>
       </c>
       <c r="C53">
-        <v>18.7622374931282</v>
+        <v>18.6159951580476</v>
       </c>
       <c r="D53">
-        <v>27.3844374931282</v>
+        <v>27.5103951580476</v>
       </c>
       <c r="E53">
-        <v>5.3622</v>
+        <v>5.634400000000001</v>
       </c>
       <c r="F53">
-        <v>13.8822</v>
+        <v>14.1544</v>
       </c>
       <c r="G53">
         <v>5.26</v>
@@ -5627,28 +5627,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M53">
-        <v>0.7190979599999999</v>
+        <v>0.7331979200000001</v>
       </c>
       <c r="N53">
-        <v>6.954235373333334</v>
+        <v>6.940135413333334</v>
       </c>
       <c r="O53">
-        <v>2.086270612</v>
+        <v>2.082040624</v>
       </c>
       <c r="P53">
-        <v>4.867964761333334</v>
+        <v>4.858094789333334</v>
       </c>
       <c r="Q53">
-        <v>5.527964761333334</v>
+        <v>5.518094789333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2774687835242565</v>
+        <v>0.2814575711193711</v>
       </c>
       <c r="T53">
-        <v>1.615297284873964</v>
+        <v>1.643108877244383</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.67077611141232</v>
+        <v>10.46556887850055</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1539548341372981</v>
+        <v>0.1534573643477106</v>
       </c>
       <c r="C54">
-        <v>18.6159951580476</v>
+        <v>18.47091688886151</v>
       </c>
       <c r="D54">
-        <v>27.5103951580476</v>
+        <v>27.63751688886151</v>
       </c>
       <c r="E54">
-        <v>5.634400000000001</v>
+        <v>5.906600000000001</v>
       </c>
       <c r="F54">
-        <v>14.1544</v>
+        <v>14.4266</v>
       </c>
       <c r="G54">
         <v>5.26</v>
@@ -5709,28 +5709,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M54">
-        <v>0.7331979200000001</v>
+        <v>0.74729788</v>
       </c>
       <c r="N54">
-        <v>6.940135413333334</v>
+        <v>6.926035453333334</v>
       </c>
       <c r="O54">
-        <v>2.082040624</v>
+        <v>2.077810636</v>
       </c>
       <c r="P54">
-        <v>4.858094789333334</v>
+        <v>4.848224817333334</v>
       </c>
       <c r="Q54">
-        <v>5.518094789333334</v>
+        <v>5.508224817333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2814575711193711</v>
+        <v>0.2856160943568311</v>
       </c>
       <c r="T54">
-        <v>1.643108877244383</v>
+        <v>1.672103941630565</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>10.46556887850055</v>
+        <v>10.26810531475526</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1534573643477106</v>
+        <v>0.152959894558123</v>
       </c>
       <c r="C55">
-        <v>18.47091688886151</v>
+        <v>18.32701889744521</v>
       </c>
       <c r="D55">
-        <v>27.63751688886151</v>
+        <v>27.76581889744521</v>
       </c>
       <c r="E55">
-        <v>5.906600000000001</v>
+        <v>6.178800000000001</v>
       </c>
       <c r="F55">
-        <v>14.4266</v>
+        <v>14.6988</v>
       </c>
       <c r="G55">
         <v>5.26</v>
@@ -5791,28 +5791,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M55">
-        <v>0.74729788</v>
+        <v>0.76139784</v>
       </c>
       <c r="N55">
-        <v>6.926035453333334</v>
+        <v>6.911935493333334</v>
       </c>
       <c r="O55">
-        <v>2.077810636</v>
+        <v>2.073580648</v>
       </c>
       <c r="P55">
-        <v>4.848224817333334</v>
+        <v>4.838354845333334</v>
       </c>
       <c r="Q55">
-        <v>5.508224817333334</v>
+        <v>5.498354845333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2856160943568311</v>
+        <v>0.2899554229524414</v>
       </c>
       <c r="T55">
-        <v>1.672103941630565</v>
+        <v>1.702359660990059</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>10.26810531475526</v>
+        <v>10.07795521633386</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.152959894558123</v>
+        <v>0.1524624247685355</v>
       </c>
       <c r="C56">
-        <v>18.32701889744521</v>
+        <v>18.18431769812045</v>
       </c>
       <c r="D56">
-        <v>27.76581889744521</v>
+        <v>27.89531769812045</v>
       </c>
       <c r="E56">
-        <v>6.178800000000001</v>
+        <v>6.451000000000001</v>
       </c>
       <c r="F56">
-        <v>14.6988</v>
+        <v>14.971</v>
       </c>
       <c r="G56">
         <v>5.26</v>
@@ -5873,28 +5873,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M56">
-        <v>0.76139784</v>
+        <v>0.7754978</v>
       </c>
       <c r="N56">
-        <v>6.911935493333334</v>
+        <v>6.897835533333334</v>
       </c>
       <c r="O56">
-        <v>2.073580648</v>
+        <v>2.06935066</v>
       </c>
       <c r="P56">
-        <v>4.838354845333334</v>
+        <v>4.828484873333334</v>
       </c>
       <c r="Q56">
-        <v>5.498354845333334</v>
+        <v>5.488484873333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2899554229524414</v>
+        <v>0.2944876105967456</v>
       </c>
       <c r="T56">
-        <v>1.702359660990059</v>
+        <v>1.733960078987753</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>10.07795521633386</v>
+        <v>9.894719666945971</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1524624247685355</v>
+        <v>0.1526313549789479</v>
       </c>
       <c r="C57">
-        <v>18.18431769812045</v>
+        <v>17.868007409627</v>
       </c>
       <c r="D57">
-        <v>27.89531769812045</v>
+        <v>27.85120740962701</v>
       </c>
       <c r="E57">
-        <v>6.451000000000001</v>
+        <v>6.723200000000002</v>
       </c>
       <c r="F57">
-        <v>14.971</v>
+        <v>15.2432</v>
       </c>
       <c r="G57">
         <v>5.26</v>
@@ -5955,45 +5955,45 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M57">
-        <v>0.7754978</v>
+        <v>0.8155112000000001</v>
       </c>
       <c r="N57">
-        <v>6.897835533333334</v>
+        <v>6.857822133333333</v>
       </c>
       <c r="O57">
-        <v>2.06935066</v>
+        <v>2.05734664</v>
       </c>
       <c r="P57">
-        <v>4.828484873333334</v>
+        <v>4.800475493333334</v>
       </c>
       <c r="Q57">
-        <v>5.488484873333334</v>
+        <v>5.460475493333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2944876105967456</v>
+        <v>0.2992258067703363</v>
       </c>
       <c r="T57">
-        <v>1.733960078987753</v>
+        <v>1.766996879621706</v>
       </c>
       <c r="U57">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>9.894719666945971</v>
+        <v>9.409231085156565</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1526313549789479</v>
+        <v>0.1521457851893604</v>
       </c>
       <c r="C58">
-        <v>17.868007409627</v>
+        <v>17.72297469601803</v>
       </c>
       <c r="D58">
-        <v>27.85120740962701</v>
+        <v>27.97837469601803</v>
       </c>
       <c r="E58">
-        <v>6.723200000000002</v>
+        <v>6.995400000000002</v>
       </c>
       <c r="F58">
-        <v>15.2432</v>
+        <v>15.5154</v>
       </c>
       <c r="G58">
         <v>5.26</v>
@@ -6037,28 +6037,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M58">
-        <v>0.8155112000000001</v>
+        <v>0.8300739</v>
       </c>
       <c r="N58">
-        <v>6.857822133333333</v>
+        <v>6.843259433333333</v>
       </c>
       <c r="O58">
-        <v>2.05734664</v>
+        <v>2.05297783</v>
       </c>
       <c r="P58">
-        <v>4.800475493333334</v>
+        <v>4.790281603333334</v>
       </c>
       <c r="Q58">
-        <v>5.460475493333334</v>
+        <v>5.450281603333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2992258067703363</v>
+        <v>0.3041843841613032</v>
       </c>
       <c r="T58">
-        <v>1.766996879621706</v>
+        <v>1.801570275633982</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>9.409231085156565</v>
+        <v>9.244156855592415</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1521457851893604</v>
+        <v>0.1516602153997728</v>
       </c>
       <c r="C59">
-        <v>17.72297469601803</v>
+        <v>17.57910858862199</v>
       </c>
       <c r="D59">
-        <v>27.97837469601803</v>
+        <v>28.10670858862199</v>
       </c>
       <c r="E59">
-        <v>6.995400000000002</v>
+        <v>7.267600000000002</v>
       </c>
       <c r="F59">
-        <v>15.5154</v>
+        <v>15.7876</v>
       </c>
       <c r="G59">
         <v>5.26</v>
@@ -6119,28 +6119,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M59">
-        <v>0.8300739</v>
+        <v>0.8446366000000001</v>
       </c>
       <c r="N59">
-        <v>6.843259433333333</v>
+        <v>6.828696733333333</v>
       </c>
       <c r="O59">
-        <v>2.05297783</v>
+        <v>2.04860902</v>
       </c>
       <c r="P59">
-        <v>4.790281603333334</v>
+        <v>4.780087713333334</v>
       </c>
       <c r="Q59">
-        <v>5.450281603333334</v>
+        <v>5.440087713333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3041843841613032</v>
+        <v>0.3093790842851734</v>
       </c>
       <c r="T59">
-        <v>1.801570275633982</v>
+        <v>1.837790023837319</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>9.244156855592415</v>
+        <v>9.084774840840822</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1516602153997728</v>
+        <v>0.1511746456101853</v>
       </c>
       <c r="C60">
-        <v>17.57910858862199</v>
+        <v>17.43642521471688</v>
       </c>
       <c r="D60">
-        <v>28.10670858862199</v>
+        <v>28.23622521471688</v>
       </c>
       <c r="E60">
-        <v>7.267599999999998</v>
+        <v>7.5398</v>
       </c>
       <c r="F60">
-        <v>15.7876</v>
+        <v>16.0598</v>
       </c>
       <c r="G60">
         <v>5.26</v>
@@ -6201,28 +6201,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M60">
-        <v>0.8446365999999998</v>
+        <v>0.8591992999999999</v>
       </c>
       <c r="N60">
-        <v>6.828696733333334</v>
+        <v>6.814134033333334</v>
       </c>
       <c r="O60">
-        <v>2.04860902</v>
+        <v>2.04424021</v>
       </c>
       <c r="P60">
-        <v>4.780087713333334</v>
+        <v>4.769893823333334</v>
       </c>
       <c r="Q60">
-        <v>5.440087713333334</v>
+        <v>5.429893823333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3093790842851734</v>
+        <v>0.314827184415086</v>
       </c>
       <c r="T60">
-        <v>1.837790023837319</v>
+        <v>1.875776589026185</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>9.084774840840826</v>
+        <v>8.930795606250301</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1511746456101853</v>
+        <v>0.1506890758205977</v>
       </c>
       <c r="C61">
-        <v>17.43642521471688</v>
+        <v>17.29494100021687</v>
       </c>
       <c r="D61">
-        <v>28.23622521471688</v>
+        <v>28.36694100021687</v>
       </c>
       <c r="E61">
-        <v>7.5398</v>
+        <v>7.811999999999998</v>
       </c>
       <c r="F61">
-        <v>16.0598</v>
+        <v>16.332</v>
       </c>
       <c r="G61">
         <v>5.26</v>
@@ -6283,28 +6283,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M61">
-        <v>0.8591992999999999</v>
+        <v>0.8737619999999998</v>
       </c>
       <c r="N61">
-        <v>6.814134033333334</v>
+        <v>6.799571333333334</v>
       </c>
       <c r="O61">
-        <v>2.04424021</v>
+        <v>2.0398714</v>
       </c>
       <c r="P61">
-        <v>4.769893823333334</v>
+        <v>4.759699933333334</v>
       </c>
       <c r="Q61">
-        <v>5.429893823333334</v>
+        <v>5.419699933333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.314827184415086</v>
+        <v>0.3205476895514943</v>
       </c>
       <c r="T61">
-        <v>1.875776589026185</v>
+        <v>1.915662482474494</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.930795606250301</v>
+        <v>8.781949012812797</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1506890758205977</v>
+        <v>0.1502035060310102</v>
       </c>
       <c r="C62">
-        <v>17.29494100021687</v>
+        <v>17.15467267661695</v>
       </c>
       <c r="D62">
-        <v>28.36694100021687</v>
+        <v>28.49887267661695</v>
       </c>
       <c r="E62">
-        <v>7.811999999999998</v>
+        <v>8.084199999999999</v>
       </c>
       <c r="F62">
-        <v>16.332</v>
+        <v>16.6042</v>
       </c>
       <c r="G62">
         <v>5.26</v>
@@ -6365,28 +6365,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M62">
-        <v>0.8737619999999998</v>
+        <v>0.8883247</v>
       </c>
       <c r="N62">
-        <v>6.799571333333334</v>
+        <v>6.785008633333334</v>
       </c>
       <c r="O62">
-        <v>2.0398714</v>
+        <v>2.03550259</v>
       </c>
       <c r="P62">
-        <v>4.759699933333334</v>
+        <v>4.749506043333334</v>
       </c>
       <c r="Q62">
-        <v>5.419699933333334</v>
+        <v>5.409506043333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3205476895514943</v>
+        <v>0.3265615539256671</v>
       </c>
       <c r="T62">
-        <v>1.915662482474494</v>
+        <v>1.957593806356049</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.781949012812797</v>
+        <v>8.63798263555357</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1502035060310102</v>
+        <v>0.1497179362414226</v>
       </c>
       <c r="C63">
-        <v>17.15467267661695</v>
+        <v>17.01563728813231</v>
       </c>
       <c r="D63">
-        <v>28.49887267661695</v>
+        <v>28.63203728813231</v>
       </c>
       <c r="E63">
-        <v>8.084199999999999</v>
+        <v>8.356400000000001</v>
       </c>
       <c r="F63">
-        <v>16.6042</v>
+        <v>16.8764</v>
       </c>
       <c r="G63">
         <v>5.26</v>
@@ -6447,28 +6447,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M63">
-        <v>0.8883247</v>
+        <v>0.9028874</v>
       </c>
       <c r="N63">
-        <v>6.785008633333334</v>
+        <v>6.770445933333334</v>
       </c>
       <c r="O63">
-        <v>2.03550259</v>
+        <v>2.03113378</v>
       </c>
       <c r="P63">
-        <v>4.749506043333334</v>
+        <v>4.739312153333334</v>
       </c>
       <c r="Q63">
-        <v>5.409506043333334</v>
+        <v>5.399312153333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3265615539256671</v>
+        <v>0.332891937477428</v>
       </c>
       <c r="T63">
-        <v>1.957593806356049</v>
+        <v>2.001732042020845</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.63798263555357</v>
+        <v>8.498660334980125</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1497179362414226</v>
+        <v>0.149232366451835</v>
       </c>
       <c r="C64">
-        <v>17.01563728813231</v>
+        <v>16.87785219903872</v>
       </c>
       <c r="D64">
-        <v>28.63203728813231</v>
+        <v>28.76645219903871</v>
       </c>
       <c r="E64">
-        <v>8.356400000000001</v>
+        <v>8.628599999999999</v>
       </c>
       <c r="F64">
-        <v>16.8764</v>
+        <v>17.1486</v>
       </c>
       <c r="G64">
         <v>5.26</v>
@@ -6529,28 +6529,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M64">
-        <v>0.9028874</v>
+        <v>0.9174500999999999</v>
       </c>
       <c r="N64">
-        <v>6.770445933333334</v>
+        <v>6.755883233333334</v>
       </c>
       <c r="O64">
-        <v>2.03113378</v>
+        <v>2.02676497</v>
       </c>
       <c r="P64">
-        <v>4.739312153333334</v>
+        <v>4.729118263333334</v>
       </c>
       <c r="Q64">
-        <v>5.399312153333334</v>
+        <v>5.389118263333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.332891937477428</v>
+        <v>0.3395645039238785</v>
       </c>
       <c r="T64">
-        <v>2.001732042020845</v>
+        <v>2.048256128262115</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>8.498660334980125</v>
+        <v>8.363760964583616</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.149232366451835</v>
+        <v>0.1487467966622475</v>
       </c>
       <c r="C65">
-        <v>16.87785219903872</v>
+        <v>16.74133510122065</v>
       </c>
       <c r="D65">
-        <v>28.76645219903871</v>
+        <v>28.90213510122065</v>
       </c>
       <c r="E65">
-        <v>8.628599999999999</v>
+        <v>8.9008</v>
       </c>
       <c r="F65">
-        <v>17.1486</v>
+        <v>17.4208</v>
       </c>
       <c r="G65">
         <v>5.26</v>
@@ -6611,28 +6611,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M65">
-        <v>0.9174500999999999</v>
+        <v>0.9320128</v>
       </c>
       <c r="N65">
-        <v>6.755883233333334</v>
+        <v>6.741320533333334</v>
       </c>
       <c r="O65">
-        <v>2.02676497</v>
+        <v>2.02239616</v>
       </c>
       <c r="P65">
-        <v>4.729118263333334</v>
+        <v>4.718924373333333</v>
       </c>
       <c r="Q65">
-        <v>5.389118263333334</v>
+        <v>5.378924373333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3395645039238785</v>
+        <v>0.3466077685062431</v>
       </c>
       <c r="T65">
-        <v>2.048256128262115</v>
+        <v>2.097364885961234</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.363760964583616</v>
+        <v>8.233077199511996</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1487467966622475</v>
+        <v>0.1482612268726599</v>
       </c>
       <c r="C66">
-        <v>16.74133510122065</v>
+        <v>16.60610402193417</v>
       </c>
       <c r="D66">
-        <v>28.90213510122065</v>
+        <v>29.03910402193417</v>
       </c>
       <c r="E66">
-        <v>8.9008</v>
+        <v>9.173000000000002</v>
       </c>
       <c r="F66">
-        <v>17.4208</v>
+        <v>17.693</v>
       </c>
       <c r="G66">
         <v>5.26</v>
@@ -6693,28 +6693,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M66">
-        <v>0.9320128</v>
+        <v>0.9465755</v>
       </c>
       <c r="N66">
-        <v>6.741320533333334</v>
+        <v>6.726757833333334</v>
       </c>
       <c r="O66">
-        <v>2.02239616</v>
+        <v>2.01802735</v>
       </c>
       <c r="P66">
-        <v>4.718924373333333</v>
+        <v>4.708730483333333</v>
       </c>
       <c r="Q66">
-        <v>5.378924373333334</v>
+        <v>5.368730483333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3466077685062431</v>
+        <v>0.354053505350457</v>
       </c>
       <c r="T66">
-        <v>2.097364885961234</v>
+        <v>2.149279858386017</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.233077199511996</v>
+        <v>8.106414473365657</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1482612268726599</v>
+        <v>0.1477756570830724</v>
       </c>
       <c r="C67">
-        <v>16.60610402193417</v>
+        <v>16.47217733179139</v>
       </c>
       <c r="D67">
-        <v>29.03910402193417</v>
+        <v>29.17737733179139</v>
       </c>
       <c r="E67">
-        <v>9.173000000000002</v>
+        <v>9.4452</v>
       </c>
       <c r="F67">
-        <v>17.693</v>
+        <v>17.9652</v>
       </c>
       <c r="G67">
         <v>5.26</v>
@@ -6775,28 +6775,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M67">
-        <v>0.9465755</v>
+        <v>0.9611381999999999</v>
       </c>
       <c r="N67">
-        <v>6.726757833333334</v>
+        <v>6.712195133333334</v>
       </c>
       <c r="O67">
-        <v>2.01802735</v>
+        <v>2.01365854</v>
       </c>
       <c r="P67">
-        <v>4.708730483333333</v>
+        <v>4.698536593333333</v>
       </c>
       <c r="Q67">
-        <v>5.368730483333334</v>
+        <v>5.358536593333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.354053505350457</v>
+        <v>0.3619372267149188</v>
       </c>
       <c r="T67">
-        <v>2.149279858386017</v>
+        <v>2.204248652718141</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.106414473365657</v>
+        <v>7.983590011647997</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1477756570830724</v>
+        <v>0.1472900872934848</v>
       </c>
       <c r="C68">
-        <v>16.47217733179139</v>
+        <v>16.33957375297432</v>
       </c>
       <c r="D68">
-        <v>29.17737733179139</v>
+        <v>29.31697375297433</v>
       </c>
       <c r="E68">
-        <v>9.4452</v>
+        <v>9.717400000000001</v>
       </c>
       <c r="F68">
-        <v>17.9652</v>
+        <v>18.2374</v>
       </c>
       <c r="G68">
         <v>5.26</v>
@@ -6857,28 +6857,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M68">
-        <v>0.9611381999999999</v>
+        <v>0.9757009</v>
       </c>
       <c r="N68">
-        <v>6.712195133333334</v>
+        <v>6.697632433333334</v>
       </c>
       <c r="O68">
-        <v>2.01365854</v>
+        <v>2.00928973</v>
       </c>
       <c r="P68">
-        <v>4.698536593333333</v>
+        <v>4.688342703333333</v>
       </c>
       <c r="Q68">
-        <v>5.358536593333334</v>
+        <v>5.348342703333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3619372267149188</v>
+        <v>0.3702987493741965</v>
       </c>
       <c r="T68">
-        <v>2.204248652718141</v>
+        <v>2.262548889130999</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.983590011647997</v>
+        <v>7.864431951772653</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1472900872934848</v>
+        <v>0.1468045175038973</v>
       </c>
       <c r="C69">
-        <v>16.33957375297432</v>
+        <v>16.20831236768556</v>
       </c>
       <c r="D69">
-        <v>29.31697375297433</v>
+        <v>29.45791236768556</v>
       </c>
       <c r="E69">
-        <v>9.717400000000001</v>
+        <v>9.989599999999999</v>
       </c>
       <c r="F69">
-        <v>18.2374</v>
+        <v>18.5096</v>
       </c>
       <c r="G69">
         <v>5.26</v>
@@ -6939,28 +6939,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M69">
-        <v>0.9757009</v>
+        <v>0.9902635999999999</v>
       </c>
       <c r="N69">
-        <v>6.697632433333334</v>
+        <v>6.683069733333334</v>
       </c>
       <c r="O69">
-        <v>2.00928973</v>
+        <v>2.00492092</v>
       </c>
       <c r="P69">
-        <v>4.688342703333333</v>
+        <v>4.678148813333334</v>
       </c>
       <c r="Q69">
-        <v>5.348342703333334</v>
+        <v>5.338148813333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3702987493741965</v>
+        <v>0.3791828671996791</v>
       </c>
       <c r="T69">
-        <v>2.262548889130999</v>
+        <v>2.32449289031966</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.864431951772653</v>
+        <v>7.748778540717174</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1468045175038973</v>
+        <v>0.1463189477143098</v>
       </c>
       <c r="C70">
-        <v>16.20831236768556</v>
+        <v>16.07841262684385</v>
       </c>
       <c r="D70">
-        <v>29.45791236768556</v>
+        <v>29.60021262684385</v>
       </c>
       <c r="E70">
-        <v>9.989599999999999</v>
+        <v>10.2618</v>
       </c>
       <c r="F70">
-        <v>18.5096</v>
+        <v>18.7818</v>
       </c>
       <c r="G70">
         <v>5.26</v>
@@ -7021,28 +7021,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M70">
-        <v>0.9902635999999999</v>
+        <v>1.0048263</v>
       </c>
       <c r="N70">
-        <v>6.683069733333334</v>
+        <v>6.668507033333334</v>
       </c>
       <c r="O70">
-        <v>2.00492092</v>
+        <v>2.00055211</v>
       </c>
       <c r="P70">
-        <v>4.678148813333334</v>
+        <v>4.667954923333334</v>
       </c>
       <c r="Q70">
-        <v>5.338148813333334</v>
+        <v>5.327954923333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3791828671996791</v>
+        <v>0.3886401539171283</v>
       </c>
       <c r="T70">
-        <v>2.32449289031966</v>
+        <v>2.390433278681785</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.748778540717174</v>
+        <v>7.63647740244591</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1463189477143098</v>
+        <v>0.1462253779247222</v>
       </c>
       <c r="C71">
-        <v>16.07841262684385</v>
+        <v>15.83379216624392</v>
       </c>
       <c r="D71">
-        <v>29.60021262684385</v>
+        <v>29.62779216624392</v>
       </c>
       <c r="E71">
-        <v>10.2618</v>
+        <v>10.534</v>
       </c>
       <c r="F71">
-        <v>18.7818</v>
+        <v>19.054</v>
       </c>
       <c r="G71">
         <v>5.26</v>
@@ -7103,45 +7103,45 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M71">
-        <v>1.0048263</v>
+        <v>1.0346322</v>
       </c>
       <c r="N71">
-        <v>6.668507033333334</v>
+        <v>6.638701133333334</v>
       </c>
       <c r="O71">
-        <v>2.00055211</v>
+        <v>1.99161034</v>
       </c>
       <c r="P71">
-        <v>4.667954923333334</v>
+        <v>4.647090793333334</v>
       </c>
       <c r="Q71">
-        <v>5.327954923333334</v>
+        <v>5.307090793333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3886401539171283</v>
+        <v>0.3987279264157407</v>
       </c>
       <c r="T71">
-        <v>2.390433278681785</v>
+        <v>2.460769692934716</v>
       </c>
       <c r="U71">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V71">
         <v>0.3</v>
       </c>
       <c r="W71">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y71">
-        <v>7.63647740244591</v>
+        <v>7.41648417025232</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1462253779247222</v>
+        <v>0.1457454081351346</v>
       </c>
       <c r="C72">
-        <v>15.83379216624392</v>
+        <v>15.70387429242972</v>
       </c>
       <c r="D72">
-        <v>29.62779216624392</v>
+        <v>29.77007429242972</v>
       </c>
       <c r="E72">
-        <v>10.534</v>
+        <v>10.8062</v>
       </c>
       <c r="F72">
-        <v>19.054</v>
+        <v>19.3262</v>
       </c>
       <c r="G72">
         <v>5.26</v>
@@ -7185,28 +7185,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M72">
-        <v>1.0346322</v>
+        <v>1.04941266</v>
       </c>
       <c r="N72">
-        <v>6.638701133333334</v>
+        <v>6.623920673333334</v>
       </c>
       <c r="O72">
-        <v>1.99161034</v>
+        <v>1.987176202</v>
       </c>
       <c r="P72">
-        <v>4.647090793333334</v>
+        <v>4.636744471333333</v>
       </c>
       <c r="Q72">
-        <v>5.307090793333334</v>
+        <v>5.296744471333334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3987279264157407</v>
+        <v>0.4095114073625333</v>
       </c>
       <c r="T72">
-        <v>2.460769692934716</v>
+        <v>2.535956894377505</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.41648417025232</v>
+        <v>7.312026646727641</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1457454081351346</v>
+        <v>0.1452654383455471</v>
       </c>
       <c r="C73">
-        <v>15.70387429242972</v>
+        <v>15.57532958146091</v>
       </c>
       <c r="D73">
-        <v>29.77007429242972</v>
+        <v>29.91372958146091</v>
       </c>
       <c r="E73">
-        <v>10.8062</v>
+        <v>11.0784</v>
       </c>
       <c r="F73">
-        <v>19.3262</v>
+        <v>19.5984</v>
       </c>
       <c r="G73">
         <v>5.26</v>
@@ -7267,28 +7267,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M73">
-        <v>1.04941266</v>
+        <v>1.06419312</v>
       </c>
       <c r="N73">
-        <v>6.623920673333334</v>
+        <v>6.609140213333334</v>
       </c>
       <c r="O73">
-        <v>1.987176202</v>
+        <v>1.982742064</v>
       </c>
       <c r="P73">
-        <v>4.636744471333333</v>
+        <v>4.626398149333334</v>
       </c>
       <c r="Q73">
-        <v>5.296744471333334</v>
+        <v>5.286398149333334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4095114073625332</v>
+        <v>0.4210651369483824</v>
       </c>
       <c r="T73">
-        <v>2.535956894377505</v>
+        <v>2.616514610209065</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.312026646727642</v>
+        <v>7.210470721078647</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1452654383455471</v>
+        <v>0.1447854685559595</v>
       </c>
       <c r="C74">
-        <v>15.57532958146091</v>
+        <v>15.44817800829011</v>
       </c>
       <c r="D74">
-        <v>29.91372958146091</v>
+        <v>30.05877800829011</v>
       </c>
       <c r="E74">
-        <v>11.0784</v>
+        <v>11.3506</v>
       </c>
       <c r="F74">
-        <v>19.5984</v>
+        <v>19.8706</v>
       </c>
       <c r="G74">
         <v>5.26</v>
@@ -7349,28 +7349,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M74">
-        <v>1.06419312</v>
+        <v>1.07897358</v>
       </c>
       <c r="N74">
-        <v>6.609140213333334</v>
+        <v>6.594359753333334</v>
       </c>
       <c r="O74">
-        <v>1.982742064</v>
+        <v>1.978307926</v>
       </c>
       <c r="P74">
-        <v>4.626398149333334</v>
+        <v>4.616051827333334</v>
       </c>
       <c r="Q74">
-        <v>5.286398149333334</v>
+        <v>5.276051827333334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4210651369483824</v>
+        <v>0.4334746983554057</v>
       </c>
       <c r="T74">
-        <v>2.616514610209065</v>
+        <v>2.70303956425037</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.210470721078647</v>
+        <v>7.111697149557021</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1447854685559595</v>
+        <v>0.144305498766372</v>
       </c>
       <c r="C75">
-        <v>15.44817800829011</v>
+        <v>15.32243993718319</v>
       </c>
       <c r="D75">
-        <v>30.05877800829011</v>
+        <v>30.20523993718319</v>
       </c>
       <c r="E75">
-        <v>11.3506</v>
+        <v>11.6228</v>
       </c>
       <c r="F75">
-        <v>19.8706</v>
+        <v>20.1428</v>
       </c>
       <c r="G75">
         <v>5.26</v>
@@ -7431,28 +7431,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M75">
-        <v>1.07897358</v>
+        <v>1.09375404</v>
       </c>
       <c r="N75">
-        <v>6.594359753333334</v>
+        <v>6.579579293333333</v>
       </c>
       <c r="O75">
-        <v>1.978307926</v>
+        <v>1.973873788</v>
       </c>
       <c r="P75">
-        <v>4.616051827333334</v>
+        <v>4.605705505333334</v>
       </c>
       <c r="Q75">
-        <v>5.276051827333334</v>
+        <v>5.265705505333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4334746983554057</v>
+        <v>0.4468388414091229</v>
       </c>
       <c r="T75">
-        <v>2.70303956425037</v>
+        <v>2.796220283987159</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>7.111697149557021</v>
+        <v>7.015593134022467</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.144305498766372</v>
+        <v>0.1438255289767844</v>
       </c>
       <c r="C76">
-        <v>15.32243993718319</v>
+        <v>15.19813613125041</v>
       </c>
       <c r="D76">
-        <v>30.20523993718319</v>
+        <v>30.35313613125041</v>
       </c>
       <c r="E76">
-        <v>11.6228</v>
+        <v>11.895</v>
       </c>
       <c r="F76">
-        <v>20.1428</v>
+        <v>20.415</v>
       </c>
       <c r="G76">
         <v>5.26</v>
@@ -7513,28 +7513,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M76">
-        <v>1.09375404</v>
+        <v>1.1085345</v>
       </c>
       <c r="N76">
-        <v>6.579579293333333</v>
+        <v>6.564798833333334</v>
       </c>
       <c r="O76">
-        <v>1.973873788</v>
+        <v>1.96943965</v>
       </c>
       <c r="P76">
-        <v>4.605705505333334</v>
+        <v>4.595359183333334</v>
       </c>
       <c r="Q76">
-        <v>5.265705505333334</v>
+        <v>5.255359183333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4468388414091229</v>
+        <v>0.4612721159071377</v>
       </c>
       <c r="T76">
-        <v>2.796220283987159</v>
+        <v>2.896855461302893</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.015593134022467</v>
+        <v>6.922051892235499</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1438255289767844</v>
+        <v>0.1433455591871969</v>
       </c>
       <c r="C77">
-        <v>15.19813613125041</v>
+        <v>15.07528776225884</v>
       </c>
       <c r="D77">
-        <v>30.35313613125041</v>
+        <v>30.50248776225884</v>
       </c>
       <c r="E77">
-        <v>11.895</v>
+        <v>12.1672</v>
       </c>
       <c r="F77">
-        <v>20.415</v>
+        <v>20.6872</v>
       </c>
       <c r="G77">
         <v>5.26</v>
@@ -7595,28 +7595,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M77">
-        <v>1.1085345</v>
+        <v>1.12331496</v>
       </c>
       <c r="N77">
-        <v>6.564798833333334</v>
+        <v>6.550018373333334</v>
       </c>
       <c r="O77">
-        <v>1.96943965</v>
+        <v>1.965005512</v>
       </c>
       <c r="P77">
-        <v>4.595359183333334</v>
+        <v>4.585012861333333</v>
       </c>
       <c r="Q77">
-        <v>5.255359183333334</v>
+        <v>5.245012861333334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4612721159071377</v>
+        <v>0.476908163279987</v>
       </c>
       <c r="T77">
-        <v>2.896855461302893</v>
+        <v>3.005876903394938</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.922051892235499</v>
+        <v>6.830972262074506</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1433455591871969</v>
+        <v>0.1428655893976093</v>
       </c>
       <c r="C78">
-        <v>15.07528776225884</v>
+        <v>14.95391642073612</v>
       </c>
       <c r="D78">
-        <v>30.50248776225884</v>
+        <v>30.65331642073613</v>
       </c>
       <c r="E78">
-        <v>12.1672</v>
+        <v>12.4394</v>
       </c>
       <c r="F78">
-        <v>20.6872</v>
+        <v>20.9594</v>
       </c>
       <c r="G78">
         <v>5.26</v>
@@ -7677,28 +7677,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M78">
-        <v>1.12331496</v>
+        <v>1.13809542</v>
       </c>
       <c r="N78">
-        <v>6.550018373333334</v>
+        <v>6.535237913333334</v>
       </c>
       <c r="O78">
-        <v>1.965005512</v>
+        <v>1.960571374</v>
       </c>
       <c r="P78">
-        <v>4.585012861333333</v>
+        <v>4.574666539333334</v>
       </c>
       <c r="Q78">
-        <v>5.245012861333334</v>
+        <v>5.234666539333334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.476908163279987</v>
+        <v>0.4939038669461275</v>
       </c>
       <c r="T78">
-        <v>3.005876903394938</v>
+        <v>3.12437847088629</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.830972262074506</v>
+        <v>6.74225833659302</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1428655893976093</v>
+        <v>0.1423856196080218</v>
       </c>
       <c r="C79">
-        <v>14.95391642073612</v>
+        <v>14.83404412637524</v>
       </c>
       <c r="D79">
-        <v>30.65331642073613</v>
+        <v>30.80564412637524</v>
       </c>
       <c r="E79">
-        <v>12.4394</v>
+        <v>12.7116</v>
       </c>
       <c r="F79">
-        <v>20.9594</v>
+        <v>21.2316</v>
       </c>
       <c r="G79">
         <v>5.26</v>
@@ -7759,28 +7759,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M79">
-        <v>1.13809542</v>
+        <v>1.15287588</v>
       </c>
       <c r="N79">
-        <v>6.535237913333334</v>
+        <v>6.520457453333334</v>
       </c>
       <c r="O79">
-        <v>1.960571374</v>
+        <v>1.956137236</v>
       </c>
       <c r="P79">
-        <v>4.574666539333334</v>
+        <v>4.564320217333334</v>
       </c>
       <c r="Q79">
-        <v>5.234666539333334</v>
+        <v>5.224320217333334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4939038669461275</v>
+        <v>0.5124446345819171</v>
       </c>
       <c r="T79">
-        <v>3.12437847088629</v>
+        <v>3.253652908149584</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.74225833659302</v>
+        <v>6.655819127149519</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1423856196080218</v>
+        <v>0.1419056498184342</v>
       </c>
       <c r="C80">
-        <v>14.83404412637524</v>
+        <v>14.71569333875118</v>
       </c>
       <c r="D80">
-        <v>30.80564412637524</v>
+        <v>30.95949333875118</v>
       </c>
       <c r="E80">
-        <v>12.7116</v>
+        <v>12.9838</v>
       </c>
       <c r="F80">
-        <v>21.2316</v>
+        <v>21.5038</v>
       </c>
       <c r="G80">
         <v>5.26</v>
@@ -7841,28 +7841,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M80">
-        <v>1.15287588</v>
+        <v>1.16765634</v>
       </c>
       <c r="N80">
-        <v>6.520457453333334</v>
+        <v>6.505676993333333</v>
       </c>
       <c r="O80">
-        <v>1.956137236</v>
+        <v>1.951703098</v>
       </c>
       <c r="P80">
-        <v>4.564320217333334</v>
+        <v>4.553973895333334</v>
       </c>
       <c r="Q80">
-        <v>5.224320217333334</v>
+        <v>5.213973895333334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5124446345819171</v>
+        <v>0.5327511896115916</v>
       </c>
       <c r="T80">
-        <v>3.253652908149584</v>
+        <v>3.395239196580811</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.655819127149519</v>
+        <v>6.571568252122309</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1419056498184342</v>
+        <v>0.1414256800288466</v>
       </c>
       <c r="C81">
-        <v>14.71569333875118</v>
+        <v>14.59888696836047</v>
       </c>
       <c r="D81">
-        <v>30.95949333875118</v>
+        <v>31.11488696836047</v>
       </c>
       <c r="E81">
-        <v>12.9838</v>
+        <v>13.256</v>
       </c>
       <c r="F81">
-        <v>21.5038</v>
+        <v>21.776</v>
       </c>
       <c r="G81">
         <v>5.26</v>
@@ -7923,28 +7923,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M81">
-        <v>1.16765634</v>
+        <v>1.1824368</v>
       </c>
       <c r="N81">
-        <v>6.505676993333333</v>
+        <v>6.490896533333334</v>
       </c>
       <c r="O81">
-        <v>1.951703098</v>
+        <v>1.94726896</v>
       </c>
       <c r="P81">
-        <v>4.553973895333334</v>
+        <v>4.543627573333334</v>
       </c>
       <c r="Q81">
-        <v>5.213973895333334</v>
+        <v>5.203627573333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5327511896115916</v>
+        <v>0.5550884001442333</v>
       </c>
       <c r="T81">
-        <v>3.395239196580811</v>
+        <v>3.55098411385516</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.571568252122309</v>
+        <v>6.489423648970781</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1414256800288466</v>
+        <v>0.1409457102392591</v>
       </c>
       <c r="C82">
-        <v>14.59888696836047</v>
+        <v>14.48364838799453</v>
       </c>
       <c r="D82">
-        <v>31.11488696836047</v>
+        <v>31.27184838799453</v>
       </c>
       <c r="E82">
-        <v>13.256</v>
+        <v>13.5282</v>
       </c>
       <c r="F82">
-        <v>21.776</v>
+        <v>22.0482</v>
       </c>
       <c r="G82">
         <v>5.26</v>
@@ -8005,28 +8005,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M82">
-        <v>1.1824368</v>
+        <v>1.19721726</v>
       </c>
       <c r="N82">
-        <v>6.490896533333334</v>
+        <v>6.476116073333333</v>
       </c>
       <c r="O82">
-        <v>1.94726896</v>
+        <v>1.942834822</v>
       </c>
       <c r="P82">
-        <v>4.543627573333334</v>
+        <v>4.533281251333333</v>
       </c>
       <c r="Q82">
-        <v>5.203627573333334</v>
+        <v>5.193281251333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5550884001442333</v>
+        <v>0.5797768959961006</v>
       </c>
       <c r="T82">
-        <v>3.55098411385516</v>
+        <v>3.723123232947862</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.489423648970781</v>
+        <v>6.409307307625462</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1409457102392591</v>
+        <v>0.1404657404496715</v>
       </c>
       <c r="C83">
-        <v>14.48364838799453</v>
+        <v>14.37000144445933</v>
       </c>
       <c r="D83">
-        <v>31.27184838799453</v>
+        <v>31.43040144445933</v>
       </c>
       <c r="E83">
-        <v>13.5282</v>
+        <v>13.8004</v>
       </c>
       <c r="F83">
-        <v>22.0482</v>
+        <v>22.3204</v>
       </c>
       <c r="G83">
         <v>5.26</v>
@@ -8087,28 +8087,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M83">
-        <v>1.19721726</v>
+        <v>1.21199772</v>
       </c>
       <c r="N83">
-        <v>6.476116073333333</v>
+        <v>6.461335613333334</v>
       </c>
       <c r="O83">
-        <v>1.942834822</v>
+        <v>1.938400684</v>
       </c>
       <c r="P83">
-        <v>4.533281251333333</v>
+        <v>4.522934929333333</v>
       </c>
       <c r="Q83">
-        <v>5.193281251333334</v>
+        <v>5.182934929333333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5797768959961006</v>
+        <v>0.607208558053731</v>
       </c>
       <c r="T83">
-        <v>3.723123232947862</v>
+        <v>3.914388920828642</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.409307307625462</v>
+        <v>6.331145023386127</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1404657404496715</v>
+        <v>0.139985770660084</v>
       </c>
       <c r="C84">
-        <v>14.37000144445933</v>
+        <v>14.25797047065324</v>
       </c>
       <c r="D84">
-        <v>31.43040144445933</v>
+        <v>31.59057047065324</v>
       </c>
       <c r="E84">
-        <v>13.8004</v>
+        <v>14.0726</v>
       </c>
       <c r="F84">
-        <v>22.3204</v>
+        <v>22.5926</v>
       </c>
       <c r="G84">
         <v>5.26</v>
@@ -8169,28 +8169,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M84">
-        <v>1.21199772</v>
+        <v>1.22677818</v>
       </c>
       <c r="N84">
-        <v>6.461335613333334</v>
+        <v>6.446555153333334</v>
       </c>
       <c r="O84">
-        <v>1.938400684</v>
+        <v>1.933966546</v>
       </c>
       <c r="P84">
-        <v>4.522934929333333</v>
+        <v>4.512588607333334</v>
       </c>
       <c r="Q84">
-        <v>5.182934929333333</v>
+        <v>5.172588607333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.607208558053731</v>
+        <v>0.6378674744710825</v>
       </c>
       <c r="T84">
-        <v>3.914388920828642</v>
+        <v>4.128156454342454</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.331145023386127</v>
+        <v>6.25486616768268</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.139985770660084</v>
+        <v>0.1395058008704965</v>
       </c>
       <c r="C85">
-        <v>14.25797047065324</v>
+        <v>14.14758029801606</v>
       </c>
       <c r="D85">
-        <v>31.59057047065324</v>
+        <v>31.75238029801606</v>
       </c>
       <c r="E85">
-        <v>14.0726</v>
+        <v>14.3448</v>
       </c>
       <c r="F85">
-        <v>22.5926</v>
+        <v>22.8648</v>
       </c>
       <c r="G85">
         <v>5.26</v>
@@ -8251,28 +8251,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M85">
-        <v>1.22677818</v>
+        <v>1.24155864</v>
       </c>
       <c r="N85">
-        <v>6.446555153333334</v>
+        <v>6.431774693333334</v>
       </c>
       <c r="O85">
-        <v>1.933966546</v>
+        <v>1.929532408</v>
       </c>
       <c r="P85">
-        <v>4.512588607333334</v>
+        <v>4.502242285333334</v>
       </c>
       <c r="Q85">
-        <v>5.172588607333334</v>
+        <v>5.162242285333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6378674744710825</v>
+        <v>0.6723587554406032</v>
       </c>
       <c r="T85">
-        <v>4.128156454342454</v>
+        <v>4.368644929545495</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.25486616768268</v>
+        <v>6.180403475210268</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1395058008704964</v>
+        <v>0.1396208310809089</v>
       </c>
       <c r="C86">
-        <v>14.14758029801607</v>
+        <v>13.83644989263918</v>
       </c>
       <c r="D86">
-        <v>31.75238029801607</v>
+        <v>31.71344989263918</v>
       </c>
       <c r="E86">
-        <v>14.3448</v>
+        <v>14.617</v>
       </c>
       <c r="F86">
-        <v>22.8648</v>
+        <v>23.137</v>
       </c>
       <c r="G86">
         <v>5.26</v>
@@ -8333,45 +8333,45 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M86">
-        <v>1.24155864</v>
+        <v>1.2794761</v>
       </c>
       <c r="N86">
-        <v>6.431774693333334</v>
+        <v>6.393857233333334</v>
       </c>
       <c r="O86">
-        <v>1.929532408</v>
+        <v>1.91815717</v>
       </c>
       <c r="P86">
-        <v>4.502242285333334</v>
+        <v>4.475700063333334</v>
       </c>
       <c r="Q86">
-        <v>5.162242285333334</v>
+        <v>5.135700063333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6723587554406026</v>
+        <v>0.7114488738727259</v>
       </c>
       <c r="T86">
-        <v>4.368644929545491</v>
+        <v>4.641198534775603</v>
       </c>
       <c r="U86">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V86">
         <v>0.3</v>
       </c>
       <c r="W86">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>6.180403475210268</v>
+        <v>5.997246320844394</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1396208310809089</v>
+        <v>0.1391478612913213</v>
       </c>
       <c r="C87">
-        <v>13.83644989263918</v>
+        <v>13.72493384956462</v>
       </c>
       <c r="D87">
-        <v>31.71344989263918</v>
+        <v>31.87413384956462</v>
       </c>
       <c r="E87">
-        <v>14.617</v>
+        <v>14.8892</v>
       </c>
       <c r="F87">
-        <v>23.137</v>
+        <v>23.4092</v>
       </c>
       <c r="G87">
         <v>5.26</v>
@@ -8415,28 +8415,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M87">
-        <v>1.2794761</v>
+        <v>1.29452876</v>
       </c>
       <c r="N87">
-        <v>6.393857233333334</v>
+        <v>6.378804573333333</v>
       </c>
       <c r="O87">
-        <v>1.91815717</v>
+        <v>1.913641372</v>
       </c>
       <c r="P87">
-        <v>4.475700063333334</v>
+        <v>4.465163201333334</v>
       </c>
       <c r="Q87">
-        <v>5.135700063333334</v>
+        <v>5.125163201333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7114488738727259</v>
+        <v>0.7561232949380094</v>
       </c>
       <c r="T87">
-        <v>4.641198534775603</v>
+        <v>4.9526883693243</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.997246320844394</v>
+        <v>5.927510898508994</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1391478612913213</v>
+        <v>0.1386748915017338</v>
       </c>
       <c r="C88">
-        <v>13.72493384956462</v>
+        <v>13.6150543878323</v>
       </c>
       <c r="D88">
-        <v>31.87413384956462</v>
+        <v>32.0364543878323</v>
       </c>
       <c r="E88">
-        <v>14.8892</v>
+        <v>15.1614</v>
       </c>
       <c r="F88">
-        <v>23.4092</v>
+        <v>23.6814</v>
       </c>
       <c r="G88">
         <v>5.26</v>
@@ -8497,28 +8497,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M88">
-        <v>1.29452876</v>
+        <v>1.30958142</v>
       </c>
       <c r="N88">
-        <v>6.378804573333333</v>
+        <v>6.363751913333334</v>
       </c>
       <c r="O88">
-        <v>1.913641372</v>
+        <v>1.909125574</v>
       </c>
       <c r="P88">
-        <v>4.465163201333334</v>
+        <v>4.454626339333334</v>
       </c>
       <c r="Q88">
-        <v>5.125163201333334</v>
+        <v>5.114626339333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7561232949380094</v>
+        <v>0.8076707038594907</v>
       </c>
       <c r="T88">
-        <v>4.9526883693243</v>
+        <v>5.312099716880491</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.927510898508994</v>
+        <v>5.85937858933073</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1386748915017338</v>
+        <v>0.1382019217121462</v>
       </c>
       <c r="C89">
-        <v>13.6150543878323</v>
+        <v>13.50683663852777</v>
       </c>
       <c r="D89">
-        <v>32.0364543878323</v>
+        <v>32.20043663852777</v>
       </c>
       <c r="E89">
-        <v>15.1614</v>
+        <v>15.4336</v>
       </c>
       <c r="F89">
-        <v>23.6814</v>
+        <v>23.9536</v>
       </c>
       <c r="G89">
         <v>5.26</v>
@@ -8579,28 +8579,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M89">
-        <v>1.30958142</v>
+        <v>1.32463408</v>
       </c>
       <c r="N89">
-        <v>6.363751913333334</v>
+        <v>6.348699253333334</v>
       </c>
       <c r="O89">
-        <v>1.909125574</v>
+        <v>1.904609776</v>
       </c>
       <c r="P89">
-        <v>4.454626339333334</v>
+        <v>4.444089477333334</v>
       </c>
       <c r="Q89">
-        <v>5.114626339333334</v>
+        <v>5.104089477333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8076707038594907</v>
+        <v>0.8678093476012188</v>
       </c>
       <c r="T89">
-        <v>5.312099716880491</v>
+        <v>5.731412955696047</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.85937858933073</v>
+        <v>5.792794741724699</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1382019217121462</v>
+        <v>0.1377289519225587</v>
       </c>
       <c r="C90">
-        <v>13.50683663852777</v>
+        <v>13.40030624992921</v>
       </c>
       <c r="D90">
-        <v>32.20043663852777</v>
+        <v>32.36610624992921</v>
       </c>
       <c r="E90">
-        <v>15.4336</v>
+        <v>15.7058</v>
       </c>
       <c r="F90">
-        <v>23.9536</v>
+        <v>24.2258</v>
       </c>
       <c r="G90">
         <v>5.26</v>
@@ -8661,28 +8661,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M90">
-        <v>1.32463408</v>
+        <v>1.33968674</v>
       </c>
       <c r="N90">
-        <v>6.348699253333334</v>
+        <v>6.333646593333333</v>
       </c>
       <c r="O90">
-        <v>1.904609776</v>
+        <v>1.900093978</v>
       </c>
       <c r="P90">
-        <v>4.444089477333334</v>
+        <v>4.433552615333333</v>
       </c>
       <c r="Q90">
-        <v>5.104089477333334</v>
+        <v>5.093552615333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8678093476012188</v>
+        <v>0.9388822902050792</v>
       </c>
       <c r="T90">
-        <v>5.731412955696047</v>
+        <v>6.22696496520534</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.792794741724699</v>
+        <v>5.727707160357005</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1377289519225587</v>
+        <v>0.1372559821329711</v>
       </c>
       <c r="C91">
-        <v>13.40030624992921</v>
+        <v>13.29548940088089</v>
       </c>
       <c r="D91">
-        <v>32.36610624992921</v>
+        <v>32.53348940088089</v>
       </c>
       <c r="E91">
-        <v>15.7058</v>
+        <v>15.978</v>
       </c>
       <c r="F91">
-        <v>24.2258</v>
+        <v>24.498</v>
       </c>
       <c r="G91">
         <v>5.26</v>
@@ -8743,28 +8743,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M91">
-        <v>1.33968674</v>
+        <v>1.3547394</v>
       </c>
       <c r="N91">
-        <v>6.333646593333333</v>
+        <v>6.318593933333334</v>
       </c>
       <c r="O91">
-        <v>1.900093978</v>
+        <v>1.89557818</v>
       </c>
       <c r="P91">
-        <v>4.433552615333333</v>
+        <v>4.423015753333334</v>
       </c>
       <c r="Q91">
-        <v>5.093552615333333</v>
+        <v>5.083015753333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9388822902050792</v>
+        <v>1.024169821329711</v>
       </c>
       <c r="T91">
-        <v>6.22696496520534</v>
+        <v>6.821627376616491</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.727707160357005</v>
+        <v>5.664065969686372</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1372559821329711</v>
+        <v>0.1367830123433836</v>
       </c>
       <c r="C92">
-        <v>13.29548940088089</v>
+        <v>13.19241281458376</v>
       </c>
       <c r="D92">
-        <v>32.53348940088089</v>
+        <v>32.70261281458376</v>
       </c>
       <c r="E92">
-        <v>15.978</v>
+        <v>16.2502</v>
       </c>
       <c r="F92">
-        <v>24.498</v>
+        <v>24.7702</v>
       </c>
       <c r="G92">
         <v>5.26</v>
@@ -8825,28 +8825,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M92">
-        <v>1.3547394</v>
+        <v>1.36979206</v>
       </c>
       <c r="N92">
-        <v>6.318593933333334</v>
+        <v>6.303541273333334</v>
       </c>
       <c r="O92">
-        <v>1.89557818</v>
+        <v>1.891062382</v>
       </c>
       <c r="P92">
-        <v>4.423015753333334</v>
+        <v>4.412478891333333</v>
       </c>
       <c r="Q92">
-        <v>5.083015753333334</v>
+        <v>5.072478891333334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.024169821329711</v>
+        <v>1.128410137148707</v>
       </c>
       <c r="T92">
-        <v>6.821627376616491</v>
+        <v>7.548436990563454</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.664065969686372</v>
+        <v>5.601823486503005</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1367830123433836</v>
+        <v>0.1363100425537961</v>
       </c>
       <c r="C93">
-        <v>13.19241281458376</v>
+        <v>13.0911037728184</v>
       </c>
       <c r="D93">
-        <v>32.70261281458376</v>
+        <v>32.8735037728184</v>
       </c>
       <c r="E93">
-        <v>16.2502</v>
+        <v>16.5224</v>
       </c>
       <c r="F93">
-        <v>24.7702</v>
+        <v>25.0424</v>
       </c>
       <c r="G93">
         <v>5.26</v>
@@ -8907,28 +8907,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M93">
-        <v>1.36979206</v>
+        <v>1.38484472</v>
       </c>
       <c r="N93">
-        <v>6.303541273333334</v>
+        <v>6.288488613333334</v>
       </c>
       <c r="O93">
-        <v>1.891062382</v>
+        <v>1.886546584</v>
       </c>
       <c r="P93">
-        <v>4.412478891333333</v>
+        <v>4.401942029333334</v>
       </c>
       <c r="Q93">
-        <v>5.072478891333334</v>
+        <v>5.061942029333334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.128410137148707</v>
+        <v>1.258710531922451</v>
       </c>
       <c r="T93">
-        <v>7.548436990563454</v>
+        <v>8.45694900799716</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.601823486503005</v>
+        <v>5.540934100780146</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1363100425537961</v>
+        <v>0.1358370727642085</v>
       </c>
       <c r="C94">
-        <v>13.0911037728184</v>
+        <v>12.9915901306163</v>
       </c>
       <c r="D94">
-        <v>32.8735037728184</v>
+        <v>33.0461901306163</v>
       </c>
       <c r="E94">
-        <v>16.5224</v>
+        <v>16.7946</v>
       </c>
       <c r="F94">
-        <v>25.0424</v>
+        <v>25.3146</v>
       </c>
       <c r="G94">
         <v>5.26</v>
@@ -8989,28 +8989,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M94">
-        <v>1.38484472</v>
+        <v>1.39989738</v>
       </c>
       <c r="N94">
-        <v>6.288488613333334</v>
+        <v>6.273435953333333</v>
       </c>
       <c r="O94">
-        <v>1.886546584</v>
+        <v>1.882030786</v>
       </c>
       <c r="P94">
-        <v>4.401942029333334</v>
+        <v>4.391405167333334</v>
       </c>
       <c r="Q94">
-        <v>5.061942029333334</v>
+        <v>5.051405167333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.258710531922451</v>
+        <v>1.426239610917265</v>
       </c>
       <c r="T94">
-        <v>8.45694900799716</v>
+        <v>9.62503588755478</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.540934100780146</v>
+        <v>5.481354164212617</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1358370727642085</v>
+        <v>0.1353641029746209</v>
       </c>
       <c r="C95">
-        <v>12.9915901306163</v>
+        <v>12.89390033139592</v>
       </c>
       <c r="D95">
-        <v>33.0461901306163</v>
+        <v>33.22070033139592</v>
       </c>
       <c r="E95">
-        <v>16.7946</v>
+        <v>17.0668</v>
       </c>
       <c r="F95">
-        <v>25.3146</v>
+        <v>25.5868</v>
       </c>
       <c r="G95">
         <v>5.26</v>
@@ -9071,28 +9071,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M95">
-        <v>1.39989738</v>
+        <v>1.41495004</v>
       </c>
       <c r="N95">
-        <v>6.273435953333333</v>
+        <v>6.258383293333334</v>
       </c>
       <c r="O95">
-        <v>1.882030786</v>
+        <v>1.877514988</v>
       </c>
       <c r="P95">
-        <v>4.391405167333334</v>
+        <v>4.380868305333333</v>
       </c>
       <c r="Q95">
-        <v>5.051405167333334</v>
+        <v>5.040868305333333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.426239610917265</v>
+        <v>1.649611716243684</v>
       </c>
       <c r="T95">
-        <v>9.62503588755478</v>
+        <v>11.18248506029827</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.481354164212617</v>
+        <v>5.42304188586993</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1353641029746209</v>
+        <v>0.1348911331850334</v>
       </c>
       <c r="C96">
-        <v>12.89390033139592</v>
+        <v>12.79806342258097</v>
       </c>
       <c r="D96">
-        <v>33.22070033139592</v>
+        <v>33.39706342258098</v>
       </c>
       <c r="E96">
-        <v>17.0668</v>
+        <v>17.339</v>
       </c>
       <c r="F96">
-        <v>25.5868</v>
+        <v>25.859</v>
       </c>
       <c r="G96">
         <v>5.26</v>
@@ -9153,28 +9153,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M96">
-        <v>1.41495004</v>
+        <v>1.4300027</v>
       </c>
       <c r="N96">
-        <v>6.258383293333334</v>
+        <v>6.243330633333334</v>
       </c>
       <c r="O96">
-        <v>1.877514988</v>
+        <v>1.87299919</v>
       </c>
       <c r="P96">
-        <v>4.380868305333333</v>
+        <v>4.370331443333334</v>
       </c>
       <c r="Q96">
-        <v>5.040868305333333</v>
+        <v>5.030331443333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.649611716243684</v>
+        <v>1.96233266370067</v>
       </c>
       <c r="T96">
-        <v>11.18248506029827</v>
+        <v>13.36291390213917</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.42304188586993</v>
+        <v>5.36595723443972</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1348911331850334</v>
+        <v>0.1344181633954458</v>
       </c>
       <c r="C97">
-        <v>12.79806342258097</v>
+        <v>12.70410907171877</v>
       </c>
       <c r="D97">
-        <v>33.39706342258098</v>
+        <v>33.57530907171877</v>
       </c>
       <c r="E97">
-        <v>17.339</v>
+        <v>17.6112</v>
       </c>
       <c r="F97">
-        <v>25.859</v>
+        <v>26.1312</v>
       </c>
       <c r="G97">
         <v>5.26</v>
@@ -9235,28 +9235,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M97">
-        <v>1.4300027</v>
+        <v>1.44505536</v>
       </c>
       <c r="N97">
-        <v>6.243330633333334</v>
+        <v>6.228277973333334</v>
       </c>
       <c r="O97">
-        <v>1.87299919</v>
+        <v>1.868483392</v>
       </c>
       <c r="P97">
-        <v>4.370331443333334</v>
+        <v>4.359794581333334</v>
       </c>
       <c r="Q97">
-        <v>5.030331443333334</v>
+        <v>5.019794581333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.96233266370067</v>
+        <v>2.43141408488615</v>
       </c>
       <c r="T97">
-        <v>13.36291390213917</v>
+        <v>16.63355716490052</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.36595723443972</v>
+        <v>5.310061846580974</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1344181633954458</v>
+        <v>0.1339451936058583</v>
       </c>
       <c r="C98">
-        <v>12.70410907171877</v>
+        <v>12.61206758311753</v>
       </c>
       <c r="D98">
-        <v>33.57530907171877</v>
+        <v>33.75546758311753</v>
       </c>
       <c r="E98">
-        <v>17.6112</v>
+        <v>17.8834</v>
       </c>
       <c r="F98">
-        <v>26.1312</v>
+        <v>26.4034</v>
       </c>
       <c r="G98">
         <v>5.26</v>
@@ -9317,28 +9317,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M98">
-        <v>1.44505536</v>
+        <v>1.46010802</v>
       </c>
       <c r="N98">
-        <v>6.228277973333334</v>
+        <v>6.213225313333334</v>
       </c>
       <c r="O98">
-        <v>1.868483392</v>
+        <v>1.863967594</v>
       </c>
       <c r="P98">
-        <v>4.359794581333334</v>
+        <v>4.349257719333334</v>
       </c>
       <c r="Q98">
-        <v>5.019794581333334</v>
+        <v>5.009257719333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.431414084886143</v>
+        <v>3.213216453528607</v>
       </c>
       <c r="T98">
-        <v>16.63355716490047</v>
+        <v>22.08462926950268</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.310061846580974</v>
+        <v>5.255318940946119</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1339451936058583</v>
+        <v>0.1334722238162707</v>
       </c>
       <c r="C99">
-        <v>12.61206758311753</v>
+        <v>12.52196991502227</v>
       </c>
       <c r="D99">
-        <v>33.75546758311753</v>
+        <v>33.93756991502227</v>
       </c>
       <c r="E99">
-        <v>17.8834</v>
+        <v>18.1556</v>
       </c>
       <c r="F99">
-        <v>26.4034</v>
+        <v>26.6756</v>
       </c>
       <c r="G99">
         <v>5.26</v>
@@ -9399,28 +9399,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M99">
-        <v>1.46010802</v>
+        <v>1.47516068</v>
       </c>
       <c r="N99">
-        <v>6.213225313333334</v>
+        <v>6.198172653333334</v>
       </c>
       <c r="O99">
-        <v>1.863967594</v>
+        <v>1.859451796</v>
       </c>
       <c r="P99">
-        <v>4.349257719333334</v>
+        <v>4.338720857333334</v>
       </c>
       <c r="Q99">
-        <v>5.009257719333334</v>
+        <v>4.998720857333334</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.213216453528607</v>
+        <v>4.776821190813531</v>
       </c>
       <c r="T99">
-        <v>22.08462926950268</v>
+        <v>32.98677347870711</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.255318940946119</v>
+        <v>5.201693237467076</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1334722238162707</v>
+        <v>0.1329992540266832</v>
       </c>
       <c r="C100">
-        <v>12.52196991502227</v>
+        <v>12.43384769734951</v>
       </c>
       <c r="D100">
-        <v>33.93756991502227</v>
+        <v>34.12164769734951</v>
       </c>
       <c r="E100">
-        <v>18.1556</v>
+        <v>18.4278</v>
       </c>
       <c r="F100">
-        <v>26.6756</v>
+        <v>26.9478</v>
       </c>
       <c r="G100">
         <v>5.26</v>
@@ -9481,28 +9481,28 @@
         <v>7.673333333333334</v>
       </c>
       <c r="M100">
-        <v>1.47516068</v>
+        <v>1.49021334</v>
       </c>
       <c r="N100">
-        <v>6.198172653333334</v>
+        <v>6.183119993333333</v>
       </c>
       <c r="O100">
-        <v>1.859451796</v>
+        <v>1.854935998</v>
       </c>
       <c r="P100">
-        <v>4.338720857333334</v>
+        <v>4.328183995333333</v>
       </c>
       <c r="Q100">
-        <v>4.998720857333334</v>
+        <v>4.988183995333333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.776821190813531</v>
+        <v>9.467635402668309</v>
       </c>
       <c r="T100">
-        <v>32.98677347870711</v>
+        <v>65.69320610632039</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.201693237467076</v>
+        <v>5.149150881533066</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1329992540266832</v>
-      </c>
-      <c r="C101">
-        <v>12.43384769734951</v>
-      </c>
-      <c r="D101">
-        <v>34.12164769734951</v>
-      </c>
-      <c r="E101">
-        <v>18.4278</v>
-      </c>
-      <c r="F101">
-        <v>26.9478</v>
-      </c>
-      <c r="G101">
-        <v>5.26</v>
-      </c>
-      <c r="H101">
-        <v>18.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.333333333333334</v>
-      </c>
-      <c r="K101">
-        <v>0.6600000000000001</v>
-      </c>
-      <c r="L101">
-        <v>7.673333333333334</v>
-      </c>
-      <c r="M101">
-        <v>1.49021334</v>
-      </c>
-      <c r="N101">
-        <v>6.183119993333333</v>
-      </c>
-      <c r="O101">
-        <v>1.854935998</v>
-      </c>
-      <c r="P101">
-        <v>4.328183995333333</v>
-      </c>
-      <c r="Q101">
-        <v>4.988183995333333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.467635402668309</v>
-      </c>
-      <c r="T101">
-        <v>65.69320610632039</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03871</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.149150881533066</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
